--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Aircraft_Cumulative_Statistics_2020.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Aircraft_Cumulative_Statistics_2020.xlsx
@@ -13,75 +13,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="48">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>CommuteAir</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>Piedmont</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-500</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A220-100</t>
+  </si>
+  <si>
+    <t>A220-300</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A320NEO</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>A330-900</t>
+  </si>
+  <si>
+    <t>A350-900</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B787-10</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -163,10 +202,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -186,40 +225,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -227,40 +266,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>17438820672</v>
+        <v>1844326772</v>
       </c>
       <c r="C2" s="0">
-        <v>31387967302</v>
+        <v>3000070718</v>
       </c>
       <c r="D2" s="0">
-        <v>555343</v>
+        <v>62100</v>
       </c>
       <c r="E2" s="0">
-        <v>163</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>143456</v>
+        <v>176750</v>
       </c>
       <c r="G2" s="0">
-        <v>2.54</v>
+        <v>3.6600000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>8.2300000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="I2" s="0">
-        <v>55.560000000000002</v>
+        <v>61.479999999999997</v>
       </c>
       <c r="J2" s="0">
-        <v>1303</v>
+        <v>339</v>
       </c>
       <c r="K2" s="0">
-        <v>4870</v>
+        <v>872.95000000000005</v>
       </c>
       <c r="L2" s="0">
-        <v>29.140000000000001</v>
+        <v>17.460000000000001</v>
       </c>
       <c r="M2" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="3">
@@ -268,40 +307,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>7753648255</v>
+        <v>2480522085</v>
       </c>
       <c r="C3" s="0">
-        <v>12924191277</v>
+        <v>4610881396</v>
       </c>
       <c r="D3" s="0">
-        <v>364472</v>
+        <v>54425</v>
       </c>
       <c r="E3" s="0">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>85228</v>
+        <v>260247</v>
       </c>
       <c r="G3" s="0">
-        <v>2.3999999999999999</v>
+        <v>3.0699999999999998</v>
       </c>
       <c r="H3" s="0">
-        <v>5.4400000000000004</v>
+        <v>4.1699999999999999</v>
       </c>
       <c r="I3" s="0">
-        <v>59.990000000000002</v>
+        <v>53.799999999999997</v>
       </c>
       <c r="J3" s="0">
-        <v>875</v>
+        <v>354</v>
       </c>
       <c r="K3" s="0">
-        <v>3650</v>
+        <v>2450.5100000000002</v>
       </c>
       <c r="L3" s="0">
-        <v>21.09</v>
+        <v>49.009999999999998</v>
       </c>
       <c r="M3" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="4">
@@ -309,40 +348,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>77062367673</v>
+        <v>1184760768</v>
       </c>
       <c r="C4" s="0">
-        <v>119568528285</v>
+        <v>1960396207</v>
       </c>
       <c r="D4" s="0">
-        <v>503998</v>
+        <v>89271</v>
       </c>
       <c r="E4" s="0">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="F4" s="0">
-        <v>613389</v>
+        <v>49199</v>
       </c>
       <c r="G4" s="0">
-        <v>2.5899999999999999</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="H4" s="0">
-        <v>7.3899999999999997</v>
+        <v>4.2800000000000002</v>
       </c>
       <c r="I4" s="0">
-        <v>64.450000000000003</v>
+        <v>60.43</v>
       </c>
       <c r="J4" s="0">
-        <v>1102</v>
+        <v>571</v>
       </c>
       <c r="K4" s="0">
-        <v>7318</v>
+        <v>1892.1099999999999</v>
       </c>
       <c r="L4" s="0">
-        <v>42.18</v>
+        <v>27.109999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>0.11</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="5">
@@ -350,40 +389,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>64509463624</v>
+        <v>16227196611</v>
       </c>
       <c r="C5" s="0">
-        <v>117434655834</v>
+        <v>27622220218</v>
       </c>
       <c r="D5" s="0">
-        <v>410654</v>
+        <v>135983</v>
       </c>
       <c r="E5" s="0">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="F5" s="0">
-        <v>580786</v>
+        <v>595842</v>
       </c>
       <c r="G5" s="0">
-        <v>2.0299999999999998</v>
+        <v>2.9300000000000002</v>
       </c>
       <c r="H5" s="0">
-        <v>5.6299999999999999</v>
+        <v>5.6600000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>54.93</v>
+        <v>58.75</v>
       </c>
       <c r="J5" s="0">
-        <v>1096</v>
+        <v>619</v>
       </c>
       <c r="K5" s="0">
-        <v>6263</v>
+        <v>1788.53</v>
       </c>
       <c r="L5" s="0">
-        <v>34.869999999999997</v>
+        <v>23.870000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="6">
@@ -391,40 +430,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>11434771444</v>
+        <v>379832495</v>
       </c>
       <c r="C6" s="0">
-        <v>16946207332</v>
+        <v>640163300</v>
       </c>
       <c r="D6" s="0">
-        <v>568665</v>
+        <v>47036</v>
       </c>
       <c r="E6" s="0">
-        <v>191</v>
+        <v>50</v>
       </c>
       <c r="F6" s="0">
-        <v>88652</v>
+        <v>32549</v>
       </c>
       <c r="G6" s="0">
-        <v>2.9700000000000002</v>
+        <v>2.3900000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>7.9199999999999999</v>
+        <v>3.5800000000000001</v>
       </c>
       <c r="I6" s="0">
-        <v>67.480000000000004</v>
+        <v>59.329999999999998</v>
       </c>
       <c r="J6" s="0">
-        <v>998</v>
+        <v>393</v>
       </c>
       <c r="K6" s="0">
-        <v>5210</v>
+        <v>2625.96</v>
       </c>
       <c r="L6" s="0">
-        <v>27.210000000000001</v>
+        <v>52.520000000000003</v>
       </c>
       <c r="M6" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.20000000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -432,40 +471,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>4569205024</v>
+        <v>4289920848</v>
       </c>
       <c r="C7" s="0">
-        <v>7543102763</v>
+        <v>7037044872</v>
       </c>
       <c r="D7" s="0">
-        <v>340854</v>
+        <v>109697</v>
       </c>
       <c r="E7" s="0">
-        <v>159</v>
+        <v>66</v>
       </c>
       <c r="F7" s="0">
-        <v>40066</v>
+        <v>221489</v>
       </c>
       <c r="G7" s="0">
-        <v>1.8100000000000001</v>
+        <v>3.4500000000000002</v>
       </c>
       <c r="H7" s="0">
-        <v>3.8599999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="I7" s="0">
-        <v>60.57</v>
+        <v>60.960000000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>837</v>
+        <v>478</v>
       </c>
       <c r="K7" s="0">
-        <v>9148</v>
+        <v>2029.7</v>
       </c>
       <c r="L7" s="0">
-        <v>43.399999999999999</v>
+        <v>30.559999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="8">
@@ -473,40 +512,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>18609443820</v>
+        <v>1411867519</v>
       </c>
       <c r="C8" s="0">
-        <v>32709399297</v>
+        <v>2406330815</v>
       </c>
       <c r="D8" s="0">
-        <v>338993</v>
+        <v>102923</v>
       </c>
       <c r="E8" s="0">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="F8" s="0">
-        <v>169073</v>
+        <v>45066</v>
       </c>
       <c r="G8" s="0">
-        <v>1.75</v>
+        <v>1.9299999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>5.3799999999999999</v>
+        <v>3.3799999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>56.890000000000001</v>
+        <v>58.670000000000002</v>
       </c>
       <c r="J8" s="0">
-        <v>1220</v>
+        <v>535</v>
       </c>
       <c r="K8" s="0">
-        <v>5404</v>
+        <v>6407.3999999999996</v>
       </c>
       <c r="L8" s="0">
-        <v>34.460000000000001</v>
+        <v>64.159999999999997</v>
       </c>
       <c r="M8" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.20999999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -514,40 +553,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>55689428774</v>
+        <v>7422076932</v>
       </c>
       <c r="C9" s="0">
-        <v>108346892246</v>
+        <v>12829911451</v>
       </c>
       <c r="D9" s="0">
-        <v>401032</v>
+        <v>136619</v>
       </c>
       <c r="E9" s="0">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="F9" s="0">
-        <v>940304</v>
+        <v>363951</v>
       </c>
       <c r="G9" s="0">
-        <v>3.48</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>6.9199999999999999</v>
+        <v>6.2199999999999998</v>
       </c>
       <c r="I9" s="0">
-        <v>51.399999999999999</v>
+        <v>57.850000000000001</v>
       </c>
       <c r="J9" s="0">
-        <v>743</v>
+        <v>464</v>
       </c>
       <c r="K9" s="0">
-        <v>4218</v>
+        <v>1676</v>
       </c>
       <c r="L9" s="0">
-        <v>27.289999999999999</v>
+        <v>22.09</v>
       </c>
       <c r="M9" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="10">
@@ -555,40 +594,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>19315111252</v>
+        <v>1350708588</v>
       </c>
       <c r="C10" s="0">
-        <v>27936759144</v>
+        <v>2747749478</v>
       </c>
       <c r="D10" s="0">
-        <v>498693</v>
+        <v>234850</v>
       </c>
       <c r="E10" s="0">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="F10" s="0">
-        <v>143251</v>
+        <v>27820</v>
       </c>
       <c r="G10" s="0">
-        <v>2.5600000000000001</v>
+        <v>2.3799999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>6.8700000000000001</v>
+        <v>5.9199999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>69.140000000000001</v>
+        <v>49.159999999999997</v>
       </c>
       <c r="J10" s="0">
-        <v>1036</v>
+        <v>907</v>
       </c>
       <c r="K10" s="0">
-        <v>4158</v>
+        <v>5863.6599999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>22.09</v>
+        <v>53.859999999999999</v>
       </c>
       <c r="M10" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.14799999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -596,40 +635,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>2513939423</v>
+        <v>8474329</v>
       </c>
       <c r="C11" s="0">
-        <v>4125066040</v>
+        <v>18604819</v>
       </c>
       <c r="D11" s="0">
-        <v>331597</v>
+        <v>68907</v>
       </c>
       <c r="E11" s="0">
-        <v>186</v>
+        <v>130</v>
       </c>
       <c r="F11" s="0">
-        <v>18472</v>
+        <v>194</v>
       </c>
       <c r="G11" s="0">
-        <v>1.48</v>
+        <v>0.71999999999999997</v>
       </c>
       <c r="H11" s="0">
-        <v>4.46</v>
+        <v>1.51</v>
       </c>
       <c r="I11" s="0">
-        <v>60.939999999999998</v>
+        <v>45.549999999999997</v>
       </c>
       <c r="J11" s="0">
-        <v>1199</v>
+        <v>738</v>
       </c>
       <c r="K11" s="0">
-        <v>4790</v>
+        <v>4420.25</v>
       </c>
       <c r="L11" s="0">
-        <v>25.710000000000001</v>
+        <v>34</v>
       </c>
       <c r="M11" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="12">
@@ -637,40 +676,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>62458287843</v>
+        <v>20335362931</v>
       </c>
       <c r="C12" s="0">
-        <v>104531177718</v>
+        <v>32444868675</v>
       </c>
       <c r="D12" s="0">
-        <v>65535</v>
+        <v>277070</v>
       </c>
       <c r="E12" s="0">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="F12" s="0">
-        <v>353827</v>
+        <v>288958</v>
       </c>
       <c r="G12" s="0">
-        <v>65535</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="H12" s="0">
-        <v>65535</v>
+        <v>5.7300000000000004</v>
       </c>
       <c r="I12" s="0">
-        <v>59.75</v>
+        <v>62.68</v>
       </c>
       <c r="J12" s="0">
-        <v>1497</v>
+        <v>844</v>
       </c>
       <c r="K12" s="0">
-        <v>7840</v>
+        <v>5284.0299999999997</v>
       </c>
       <c r="L12" s="0">
-        <v>40.950000000000003</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="M12" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="13">
@@ -678,40 +717,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>414983325</v>
+        <v>38840353469</v>
       </c>
       <c r="C13" s="0">
-        <v>646085400</v>
+        <v>62167519813</v>
       </c>
       <c r="D13" s="0">
-        <v>174147</v>
+        <v>357490</v>
       </c>
       <c r="E13" s="0">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="F13" s="0">
-        <v>33234</v>
+        <v>389141</v>
       </c>
       <c r="G13" s="0">
-        <v>8.9600000000000009</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="H13" s="0">
-        <v>14.15</v>
+        <v>5.7599999999999998</v>
       </c>
       <c r="I13" s="0">
-        <v>64.230000000000004</v>
+        <v>62.479999999999997</v>
       </c>
       <c r="J13" s="0">
-        <v>389</v>
+        <v>977</v>
       </c>
       <c r="K13" s="0">
-        <v>483</v>
+        <v>5300.2299999999996</v>
       </c>
       <c r="L13" s="0">
-        <v>9.6600000000000001</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="M13" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="14">
@@ -719,40 +758,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>2997269011</v>
+        <v>10730245543</v>
       </c>
       <c r="C14" s="0">
-        <v>5983966046</v>
+        <v>16149429385</v>
       </c>
       <c r="D14" s="0">
-        <v>95392</v>
+        <v>506569</v>
       </c>
       <c r="E14" s="0">
-        <v>69</v>
+        <v>185</v>
       </c>
       <c r="F14" s="0">
-        <v>210808</v>
+        <v>84719</v>
       </c>
       <c r="G14" s="0">
-        <v>3.3599999999999999</v>
+        <v>2.6600000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>4.8399999999999999</v>
+        <v>7.1900000000000004</v>
       </c>
       <c r="I14" s="0">
-        <v>50.090000000000003</v>
+        <v>66.439999999999998</v>
       </c>
       <c r="J14" s="0">
-        <v>404</v>
+        <v>1030</v>
       </c>
       <c r="K14" s="0">
-        <v>1571</v>
+        <v>4935.4799999999996</v>
       </c>
       <c r="L14" s="0">
-        <v>22.600000000000001</v>
+        <v>26.66</v>
       </c>
       <c r="M14" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="15">
@@ -760,40 +799,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>4017921985</v>
+        <v>47056720011</v>
       </c>
       <c r="C15" s="0">
-        <v>6230870466</v>
+        <v>75649435807</v>
       </c>
       <c r="D15" s="0">
-        <v>48373</v>
+        <v>518893</v>
       </c>
       <c r="E15" s="0">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="F15" s="0">
-        <v>171935</v>
+        <v>335079</v>
       </c>
       <c r="G15" s="0">
-        <v>1.3300000000000001</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H15" s="0">
-        <v>2.3799999999999999</v>
+        <v>7.04</v>
       </c>
       <c r="I15" s="0">
-        <v>64.480000000000004</v>
+        <v>62.200000000000003</v>
       </c>
       <c r="J15" s="0">
-        <v>531</v>
+        <v>1211</v>
       </c>
       <c r="K15" s="0">
-        <v>1856</v>
+        <v>6175.2200000000003</v>
       </c>
       <c r="L15" s="0">
-        <v>27.760000000000002</v>
+        <v>32.969999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.084000000000000005</v>
       </c>
     </row>
     <row r="16">
@@ -801,40 +840,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>491846976</v>
+        <v>4515672524</v>
       </c>
       <c r="C16" s="0">
-        <v>801012666</v>
+        <v>8060084515</v>
       </c>
       <c r="D16" s="0">
-        <v>51281</v>
+        <v>504386</v>
       </c>
       <c r="E16" s="0">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="F16" s="0">
-        <v>37699</v>
+        <v>26025</v>
       </c>
       <c r="G16" s="0">
-        <v>2.4100000000000001</v>
+        <v>1.6299999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>3.6600000000000001</v>
+        <v>6.21</v>
       </c>
       <c r="I16" s="0">
-        <v>61.399999999999999</v>
+        <v>56.030000000000001</v>
       </c>
       <c r="J16" s="0">
-        <v>399</v>
+        <v>1606</v>
       </c>
       <c r="K16" s="0">
-        <v>2640</v>
+        <v>7006.9300000000003</v>
       </c>
       <c r="L16" s="0">
-        <v>49.689999999999998</v>
+        <v>36.340000000000003</v>
       </c>
       <c r="M16" s="0">
-        <v>0.19</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="17">
@@ -842,40 +881,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1367770965</v>
+        <v>2681705993</v>
       </c>
       <c r="C17" s="0">
-        <v>2473512264</v>
+        <v>4810620682</v>
       </c>
       <c r="D17" s="0">
-        <v>223040</v>
+        <v>132597</v>
       </c>
       <c r="E17" s="0">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F17" s="0">
-        <v>44392</v>
+        <v>114493</v>
       </c>
       <c r="G17" s="0">
-        <v>4</v>
+        <v>3.1600000000000001</v>
       </c>
       <c r="H17" s="0">
-        <v>8.4100000000000001</v>
+        <v>4.1600000000000001</v>
       </c>
       <c r="I17" s="0">
-        <v>55.299999999999997</v>
+        <v>55.75</v>
       </c>
       <c r="J17" s="0">
-        <v>733</v>
+        <v>378</v>
       </c>
       <c r="K17" s="0">
-        <v>818</v>
+        <v>5609.7399999999998</v>
       </c>
       <c r="L17" s="0">
-        <v>10.76</v>
+        <v>50.079999999999998</v>
       </c>
       <c r="M17" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.17599999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -883,40 +922,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>4299817607</v>
+        <v>35489506247</v>
       </c>
       <c r="C18" s="0">
-        <v>6523308419</v>
+        <v>66891812806</v>
       </c>
       <c r="D18" s="0">
-        <v>196900</v>
+        <v>326079</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="F18" s="0">
-        <v>139183</v>
+        <v>686453</v>
       </c>
       <c r="G18" s="0">
-        <v>4.2000000000000002</v>
+        <v>3.3500000000000001</v>
       </c>
       <c r="H18" s="0">
-        <v>8.0399999999999991</v>
+        <v>6.3200000000000003</v>
       </c>
       <c r="I18" s="0">
-        <v>65.909999999999997</v>
+        <v>53.060000000000002</v>
       </c>
       <c r="J18" s="0">
-        <v>619</v>
+        <v>688</v>
       </c>
       <c r="K18" s="0">
-        <v>1409</v>
+        <v>4492.6300000000001</v>
       </c>
       <c r="L18" s="0">
-        <v>18.620000000000001</v>
+        <v>31.719999999999999</v>
       </c>
       <c r="M18" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="19">
@@ -924,40 +963,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>574409931</v>
+        <v>69986524458</v>
       </c>
       <c r="C19" s="0">
-        <v>993152350</v>
+        <v>121168904295</v>
       </c>
       <c r="D19" s="0">
-        <v>65535</v>
+        <v>471640</v>
       </c>
       <c r="E19" s="0">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="F19" s="0">
-        <v>69034</v>
+        <v>715601</v>
       </c>
       <c r="G19" s="0">
-        <v>65535</v>
+        <v>2.79</v>
       </c>
       <c r="H19" s="0">
-        <v>65535</v>
+        <v>7.21</v>
       </c>
       <c r="I19" s="0">
-        <v>57.840000000000003</v>
+        <v>57.759999999999998</v>
       </c>
       <c r="J19" s="0">
-        <v>288</v>
+        <v>1002</v>
       </c>
       <c r="K19" s="0">
-        <v>0</v>
+        <v>5272.1800000000003</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>31.210000000000001</v>
       </c>
       <c r="M19" s="0">
-        <v>0</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="20">
@@ -965,40 +1004,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>3542066616</v>
+        <v>934888</v>
       </c>
       <c r="C20" s="0">
-        <v>5516038607</v>
+        <v>1131072</v>
       </c>
       <c r="D20" s="0">
-        <v>109337</v>
+        <v>87</v>
       </c>
       <c r="E20" s="0">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="F20" s="0">
-        <v>187945</v>
+        <v>6</v>
       </c>
       <c r="G20" s="0">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>5.9000000000000004</v>
+        <v>0</v>
       </c>
       <c r="I20" s="0">
-        <v>64.209999999999994</v>
+        <v>82.659999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>416</v>
+        <v>1096</v>
       </c>
       <c r="K20" s="0">
-        <v>2014</v>
+        <v>4862165.9800000004</v>
       </c>
       <c r="L20" s="0">
-        <v>28.559999999999999</v>
+        <v>28268.41</v>
       </c>
       <c r="M20" s="0">
-        <v>0.11</v>
+        <v>73.293000000000006</v>
       </c>
     </row>
     <row r="21">
@@ -1006,40 +1045,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>5082775801</v>
+        <v>1043583453</v>
       </c>
       <c r="C21" s="0">
-        <v>8885930759</v>
+        <v>1575251693</v>
       </c>
       <c r="D21" s="0">
-        <v>115883</v>
+        <v>365488</v>
       </c>
       <c r="E21" s="0">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="F21" s="0">
-        <v>214926</v>
+        <v>8899</v>
       </c>
       <c r="G21" s="0">
-        <v>2.7999999999999998</v>
+        <v>2.0600000000000001</v>
       </c>
       <c r="H21" s="0">
-        <v>5.2000000000000002</v>
+        <v>5.4900000000000002</v>
       </c>
       <c r="I21" s="0">
-        <v>57.200000000000003</v>
+        <v>66.25</v>
       </c>
       <c r="J21" s="0">
-        <v>556</v>
+        <v>992</v>
       </c>
       <c r="K21" s="0">
-        <v>2074</v>
+        <v>7540.5900000000001</v>
       </c>
       <c r="L21" s="0">
-        <v>27.870000000000001</v>
+        <v>42.270000000000003</v>
       </c>
       <c r="M21" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="22">
@@ -1047,40 +1086,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>11039774294</v>
+        <v>32660225447</v>
       </c>
       <c r="C22" s="0">
-        <v>19646811185</v>
+        <v>56047238877</v>
       </c>
       <c r="D22" s="0">
-        <v>133136</v>
+        <v>462398</v>
       </c>
       <c r="E22" s="0">
-        <v>64</v>
+        <v>179</v>
       </c>
       <c r="F22" s="0">
-        <v>590871</v>
+        <v>244968</v>
       </c>
       <c r="G22" s="0">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="H22" s="0">
-        <v>6.6600000000000001</v>
+        <v>6.4100000000000001</v>
       </c>
       <c r="I22" s="0">
-        <v>56.189999999999998</v>
+        <v>58.270000000000003</v>
       </c>
       <c r="J22" s="0">
-        <v>501</v>
+        <v>1278</v>
       </c>
       <c r="K22" s="0">
-        <v>2112</v>
+        <v>4849.1999999999998</v>
       </c>
       <c r="L22" s="0">
-        <v>32.210000000000001</v>
+        <v>27.09</v>
       </c>
       <c r="M22" s="0">
-        <v>0.11</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="23">
@@ -1088,40 +1127,573 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
+        <v>13157247322</v>
+      </c>
+      <c r="C23" s="0">
+        <v>21851085570</v>
+      </c>
+      <c r="D23" s="0">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0">
+        <v>186</v>
+      </c>
+      <c r="F23" s="0">
+        <v>80157</v>
+      </c>
+      <c r="G23" s="0">
+        <v>0</v>
+      </c>
+      <c r="H23" s="0">
+        <v>0</v>
+      </c>
+      <c r="I23" s="0">
+        <v>60.210000000000001</v>
+      </c>
+      <c r="J23" s="0">
+        <v>1484</v>
+      </c>
+      <c r="K23" s="0">
+        <v>6082.7600000000002</v>
+      </c>
+      <c r="L23" s="0">
+        <v>33.060000000000002</v>
+      </c>
+      <c r="M23" s="0">
+        <v>0.080000000000000002</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>3872373763</v>
+      </c>
+      <c r="C24" s="0">
+        <v>6172407107</v>
+      </c>
+      <c r="D24" s="0">
+        <v>458915</v>
+      </c>
+      <c r="E24" s="0">
+        <v>234</v>
+      </c>
+      <c r="F24" s="0">
+        <v>19128</v>
+      </c>
+      <c r="G24" s="0">
+        <v>1.4199999999999999</v>
+      </c>
+      <c r="H24" s="0">
+        <v>4.7800000000000002</v>
+      </c>
+      <c r="I24" s="0">
+        <v>62.740000000000002</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1380</v>
+      </c>
+      <c r="K24" s="0">
+        <v>6560.54</v>
+      </c>
+      <c r="L24" s="0">
+        <v>28.050000000000001</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.068000000000000005</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>7556513617</v>
+      </c>
+      <c r="C25" s="0">
+        <v>11549571538</v>
+      </c>
+      <c r="D25" s="0">
+        <v>361376</v>
+      </c>
+      <c r="E25" s="0">
+        <v>213</v>
+      </c>
+      <c r="F25" s="0">
+        <v>20732</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0.65000000000000002</v>
+      </c>
+      <c r="H25" s="0">
+        <v>3.75</v>
+      </c>
+      <c r="I25" s="0">
+        <v>65.430000000000007</v>
+      </c>
+      <c r="J25" s="0">
+        <v>2632</v>
+      </c>
+      <c r="K25" s="0">
+        <v>8337.2000000000007</v>
+      </c>
+      <c r="L25" s="0">
+        <v>39.380000000000003</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.085999999999999993</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>2665252729</v>
+      </c>
+      <c r="C26" s="0">
+        <v>4329066272</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0">
+        <v>238</v>
+      </c>
+      <c r="F26" s="0">
+        <v>6200</v>
+      </c>
+      <c r="G26" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0</v>
+      </c>
+      <c r="I26" s="0">
+        <v>61.57</v>
+      </c>
+      <c r="J26" s="0">
+        <v>2934</v>
+      </c>
+      <c r="K26" s="0">
+        <v>7817.4399999999996</v>
+      </c>
+      <c r="L26" s="0">
+        <v>32.850000000000001</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.070999999999999994</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>4799955587</v>
+      </c>
+      <c r="C27" s="0">
+        <v>7642475656</v>
+      </c>
+      <c r="D27" s="0">
+        <v>557032</v>
+      </c>
+      <c r="E27" s="0">
+        <v>254</v>
+      </c>
+      <c r="F27" s="0">
+        <v>9764</v>
+      </c>
+      <c r="G27" s="0">
+        <v>0.70999999999999996</v>
+      </c>
+      <c r="H27" s="0">
+        <v>4.7199999999999998</v>
+      </c>
+      <c r="I27" s="0">
+        <v>62.810000000000002</v>
+      </c>
+      <c r="J27" s="0">
+        <v>3086</v>
+      </c>
+      <c r="K27" s="0">
+        <v>10698.76</v>
+      </c>
+      <c r="L27" s="0">
+        <v>42.189999999999998</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.090999999999999998</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>5094388946</v>
+      </c>
+      <c r="C28" s="0">
+        <v>9550626252</v>
+      </c>
+      <c r="D28" s="0">
+        <v>816293</v>
+      </c>
+      <c r="E28" s="0">
+        <v>289</v>
+      </c>
+      <c r="F28" s="0">
+        <v>9177</v>
+      </c>
+      <c r="G28" s="0">
+        <v>0.78000000000000003</v>
+      </c>
+      <c r="H28" s="0">
+        <v>5.9299999999999997</v>
+      </c>
+      <c r="I28" s="0">
+        <v>53.340000000000003</v>
+      </c>
+      <c r="J28" s="0">
+        <v>3603</v>
+      </c>
+      <c r="K28" s="0">
+        <v>8768.4799999999996</v>
+      </c>
+      <c r="L28" s="0">
+        <v>30.350000000000001</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.064000000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>773571332</v>
+      </c>
+      <c r="C29" s="0">
+        <v>1830084789</v>
+      </c>
+      <c r="D29" s="0">
+        <v>871469</v>
+      </c>
+      <c r="E29" s="0">
+        <v>277</v>
+      </c>
+      <c r="F29" s="0">
+        <v>1345</v>
+      </c>
+      <c r="G29" s="0">
+        <v>0.64000000000000001</v>
+      </c>
+      <c r="H29" s="0">
+        <v>6.4000000000000004</v>
+      </c>
+      <c r="I29" s="0">
+        <v>42.270000000000003</v>
+      </c>
+      <c r="J29" s="0">
+        <v>4912</v>
+      </c>
+      <c r="K29" s="0">
+        <v>9192.6700000000001</v>
+      </c>
+      <c r="L29" s="0">
+        <v>33.189999999999998</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.068000000000000005</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>2604399457</v>
+      </c>
+      <c r="C30" s="0">
+        <v>6084918714</v>
+      </c>
+      <c r="D30" s="0">
+        <v>1236772</v>
+      </c>
+      <c r="E30" s="0">
+        <v>302</v>
+      </c>
+      <c r="F30" s="0">
+        <v>3626</v>
+      </c>
+      <c r="G30" s="0">
+        <v>0.73999999999999999</v>
+      </c>
+      <c r="H30" s="0">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="I30" s="0">
+        <v>42.799999999999997</v>
+      </c>
+      <c r="J30" s="0">
+        <v>5549</v>
+      </c>
+      <c r="K30" s="0">
+        <v>10350.969999999999</v>
+      </c>
+      <c r="L30" s="0">
+        <v>34.219999999999999</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>3315797016</v>
+      </c>
+      <c r="C31" s="0">
+        <v>7317275196</v>
+      </c>
+      <c r="D31" s="0">
+        <v>715276</v>
+      </c>
+      <c r="E31" s="0">
+        <v>229</v>
+      </c>
+      <c r="F31" s="0">
+        <v>9472</v>
+      </c>
+      <c r="G31" s="0">
+        <v>0.93000000000000005</v>
+      </c>
+      <c r="H31" s="0">
+        <v>6.4400000000000004</v>
+      </c>
+      <c r="I31" s="0">
+        <v>45.310000000000002</v>
+      </c>
+      <c r="J31" s="0">
+        <v>3420</v>
+      </c>
+      <c r="K31" s="0">
+        <v>12721.77</v>
+      </c>
+      <c r="L31" s="0">
+        <v>56.280000000000001</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>7558522549</v>
+      </c>
+      <c r="C32" s="0">
+        <v>15224529400</v>
+      </c>
+      <c r="D32" s="0">
+        <v>880031</v>
+      </c>
+      <c r="E32" s="0">
+        <v>261</v>
+      </c>
+      <c r="F32" s="0">
+        <v>12242</v>
+      </c>
+      <c r="G32" s="0">
+        <v>0.70999999999999996</v>
+      </c>
+      <c r="H32" s="0">
+        <v>6.75</v>
+      </c>
+      <c r="I32" s="0">
+        <v>49.649999999999999</v>
+      </c>
+      <c r="J32" s="0">
+        <v>4832</v>
+      </c>
+      <c r="K32" s="0">
+        <v>14359.98</v>
+      </c>
+      <c r="L32" s="0">
+        <v>55.759999999999998</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>3066967260</v>
+      </c>
+      <c r="C33" s="0">
+        <v>7734723540</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1670567</v>
+      </c>
+      <c r="E33" s="0">
+        <v>318</v>
+      </c>
+      <c r="F33" s="0">
+        <v>6484</v>
+      </c>
+      <c r="G33" s="0">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="H33" s="0">
+        <v>10.49</v>
+      </c>
+      <c r="I33" s="0">
+        <v>39.649999999999999</v>
+      </c>
+      <c r="J33" s="0">
+        <v>3751</v>
+      </c>
+      <c r="K33" s="0">
+        <v>8718.8600000000006</v>
+      </c>
+      <c r="L33" s="0">
+        <v>27.420000000000002</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>14259736782</v>
+      </c>
+      <c r="C34" s="0">
+        <v>22303477341</v>
+      </c>
+      <c r="D34" s="0">
+        <v>550160</v>
+      </c>
+      <c r="E34" s="0">
+        <v>301</v>
+      </c>
+      <c r="F34" s="0">
+        <v>22799</v>
+      </c>
+      <c r="G34" s="0">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H34" s="0">
+        <v>3.9199999999999999</v>
+      </c>
+      <c r="I34" s="0">
+        <v>63.939999999999998</v>
+      </c>
+      <c r="J34" s="0">
+        <v>3366</v>
+      </c>
+      <c r="K34" s="0">
+        <v>13874.34</v>
+      </c>
+      <c r="L34" s="0">
+        <v>47.590000000000003</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.099000000000000005</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>6517876044</v>
+      </c>
+      <c r="C35" s="0">
+        <v>11724723131</v>
+      </c>
+      <c r="D35" s="0">
+        <v>934241</v>
+      </c>
+      <c r="E35" s="0">
+        <v>306</v>
+      </c>
+      <c r="F35" s="0">
+        <v>7956</v>
+      </c>
+      <c r="G35" s="0">
+        <v>0.63</v>
+      </c>
+      <c r="H35" s="0">
+        <v>6</v>
+      </c>
+      <c r="I35" s="0">
+        <v>55.590000000000003</v>
+      </c>
+      <c r="J35" s="0">
+        <v>4744</v>
+      </c>
+      <c r="K35" s="0">
+        <v>20396.029999999999</v>
+      </c>
+      <c r="L35" s="0">
+        <v>65.739999999999995</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
         <v>375183124315</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C36" s="0">
         <v>641154635400</v>
       </c>
-      <c r="D23" s="0">
-        <v>65535</v>
-      </c>
-      <c r="E23" s="0">
+      <c r="D36" s="0">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0">
         <v>130</v>
       </c>
-      <c r="F23" s="0">
+      <c r="F36" s="0">
         <v>4876531</v>
       </c>
-      <c r="G23" s="0">
-        <v>65535</v>
-      </c>
-      <c r="H23" s="0">
-        <v>65535</v>
-      </c>
-      <c r="I23" s="0">
+      <c r="G36" s="0">
+        <v>0</v>
+      </c>
+      <c r="H36" s="0">
+        <v>0</v>
+      </c>
+      <c r="I36" s="0">
         <v>58.520000000000003</v>
       </c>
-      <c r="J23" s="0">
+      <c r="J36" s="0">
         <v>849</v>
       </c>
-      <c r="K23" s="0">
-        <v>4920</v>
-      </c>
-      <c r="L23" s="0">
+      <c r="K36" s="0">
+        <v>4920.4300000000003</v>
+      </c>
+      <c r="L36" s="0">
         <v>33.520000000000003</v>
       </c>
-      <c r="M23" s="0">
-        <v>0.089999999999999997</v>
+      <c r="M36" s="0">
+        <v>0.086999999999999994</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Aircraft_Cumulative_Statistics_2020.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Aircraft_Cumulative_Statistics_2020.xlsx
@@ -13,11 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="53" uniqueCount="53">
   <si>
     <t>Row</t>
   </si>
   <si>
+    <t>E140</t>
+  </si>
+  <si>
     <t>E145</t>
   </si>
   <si>
@@ -30,7 +33,10 @@
     <t>E175</t>
   </si>
   <si>
-    <t>CRJ-500</t>
+    <t>Q400</t>
+  </si>
+  <si>
+    <t>CRJ-550</t>
   </si>
   <si>
     <t>CRJ-700</t>
@@ -63,7 +69,16 @@
     <t>A321NEO</t>
   </si>
   <si>
+    <t>MD-80</t>
+  </si>
+  <si>
+    <t>MD-90</t>
+  </si>
+  <si>
     <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -202,7 +217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -225,40 +240,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
@@ -266,40 +281,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>1844326772</v>
+        <v>382980390</v>
       </c>
       <c r="C2" s="0">
-        <v>3000070718</v>
+        <v>609744433</v>
       </c>
       <c r="D2" s="0">
-        <v>62100</v>
+        <v>24091</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F2" s="0">
-        <v>176750</v>
+        <v>40693</v>
       </c>
       <c r="G2" s="0">
-        <v>3.6600000000000001</v>
+        <v>1.6100000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>5.25</v>
+        <v>2.29</v>
       </c>
       <c r="I2" s="0">
-        <v>61.479999999999997</v>
+        <v>62.810000000000002</v>
       </c>
       <c r="J2" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K2" s="0">
-        <v>872.95000000000005</v>
+        <v>1756.73</v>
       </c>
       <c r="L2" s="0">
-        <v>17.460000000000001</v>
+        <v>39.93</v>
       </c>
       <c r="M2" s="0">
-        <v>0.073999999999999996</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -307,40 +322,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>2480522085</v>
+        <v>1844326772</v>
       </c>
       <c r="C3" s="0">
-        <v>4610881396</v>
+        <v>3000070718</v>
       </c>
       <c r="D3" s="0">
-        <v>54425</v>
+        <v>62100</v>
       </c>
       <c r="E3" s="0">
         <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>260247</v>
+        <v>176750</v>
       </c>
       <c r="G3" s="0">
-        <v>3.0699999999999998</v>
+        <v>3.6600000000000001</v>
       </c>
       <c r="H3" s="0">
-        <v>4.1699999999999999</v>
+        <v>5.25</v>
       </c>
       <c r="I3" s="0">
-        <v>53.799999999999997</v>
+        <v>61.479999999999997</v>
       </c>
       <c r="J3" s="0">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="K3" s="0">
-        <v>2450.5100000000002</v>
+        <v>872.95000000000005</v>
       </c>
       <c r="L3" s="0">
-        <v>49.009999999999998</v>
+        <v>17.460000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.188</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="4">
@@ -348,40 +363,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>1184760768</v>
+        <v>2480522085</v>
       </c>
       <c r="C4" s="0">
-        <v>1960396207</v>
+        <v>4610881396</v>
       </c>
       <c r="D4" s="0">
-        <v>89271</v>
+        <v>54425</v>
       </c>
       <c r="E4" s="0">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F4" s="0">
-        <v>49199</v>
+        <v>260247</v>
       </c>
       <c r="G4" s="0">
-        <v>2.2400000000000002</v>
+        <v>3.0699999999999998</v>
       </c>
       <c r="H4" s="0">
-        <v>4.2800000000000002</v>
+        <v>4.1699999999999999</v>
       </c>
       <c r="I4" s="0">
-        <v>60.43</v>
+        <v>53.799999999999997</v>
       </c>
       <c r="J4" s="0">
-        <v>571</v>
+        <v>354</v>
       </c>
       <c r="K4" s="0">
-        <v>1892.1099999999999</v>
+        <v>2450.5100000000002</v>
       </c>
       <c r="L4" s="0">
-        <v>27.109999999999999</v>
+        <v>49.009999999999998</v>
       </c>
       <c r="M4" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="5">
@@ -389,40 +404,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>16227196611</v>
+        <v>1184760768</v>
       </c>
       <c r="C5" s="0">
-        <v>27622220218</v>
+        <v>1960396207</v>
       </c>
       <c r="D5" s="0">
-        <v>135983</v>
+        <v>89271</v>
       </c>
       <c r="E5" s="0">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F5" s="0">
-        <v>595842</v>
+        <v>49199</v>
       </c>
       <c r="G5" s="0">
-        <v>2.9300000000000002</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="H5" s="0">
-        <v>5.6600000000000001</v>
+        <v>4.2800000000000002</v>
       </c>
       <c r="I5" s="0">
-        <v>58.75</v>
+        <v>60.43</v>
       </c>
       <c r="J5" s="0">
-        <v>619</v>
+        <v>571</v>
       </c>
       <c r="K5" s="0">
-        <v>1788.53</v>
+        <v>1892.1099999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>23.870000000000001</v>
+        <v>27.109999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.073999999999999996</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="6">
@@ -430,40 +445,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>379832495</v>
+        <v>16227196611</v>
       </c>
       <c r="C6" s="0">
-        <v>640163300</v>
+        <v>27622220218</v>
       </c>
       <c r="D6" s="0">
-        <v>47036</v>
+        <v>135983</v>
       </c>
       <c r="E6" s="0">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F6" s="0">
-        <v>32549</v>
+        <v>595842</v>
       </c>
       <c r="G6" s="0">
-        <v>2.3900000000000001</v>
+        <v>2.9300000000000002</v>
       </c>
       <c r="H6" s="0">
-        <v>3.5800000000000001</v>
+        <v>5.6600000000000001</v>
       </c>
       <c r="I6" s="0">
-        <v>59.329999999999998</v>
+        <v>58.75</v>
       </c>
       <c r="J6" s="0">
-        <v>393</v>
+        <v>619</v>
       </c>
       <c r="K6" s="0">
-        <v>2625.96</v>
+        <v>1788.53</v>
       </c>
       <c r="L6" s="0">
-        <v>52.520000000000003</v>
+        <v>23.870000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="7">
@@ -471,40 +486,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>4289920848</v>
+        <v>519978038</v>
       </c>
       <c r="C7" s="0">
-        <v>7037044872</v>
+        <v>1023062828</v>
       </c>
       <c r="D7" s="0">
-        <v>109697</v>
+        <v>95524</v>
       </c>
       <c r="E7" s="0">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F7" s="0">
-        <v>221489</v>
+        <v>50388</v>
       </c>
       <c r="G7" s="0">
-        <v>3.4500000000000002</v>
+        <v>4.7000000000000002</v>
       </c>
       <c r="H7" s="0">
-        <v>5.75</v>
+        <v>5.6100000000000003</v>
       </c>
       <c r="I7" s="0">
-        <v>60.960000000000001</v>
+        <v>50.829999999999998</v>
       </c>
       <c r="J7" s="0">
-        <v>478</v>
+        <v>267</v>
       </c>
       <c r="K7" s="0">
-        <v>2029.7</v>
+        <v>2250.02</v>
       </c>
       <c r="L7" s="0">
-        <v>30.559999999999999</v>
+        <v>29.609999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.106</v>
+        <v>0.13200000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -512,40 +527,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>1411867519</v>
+        <v>379832495</v>
       </c>
       <c r="C8" s="0">
-        <v>2406330815</v>
+        <v>640163300</v>
       </c>
       <c r="D8" s="0">
-        <v>102923</v>
+        <v>47036</v>
       </c>
       <c r="E8" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F8" s="0">
-        <v>45066</v>
+        <v>32549</v>
       </c>
       <c r="G8" s="0">
-        <v>1.9299999999999999</v>
+        <v>2.3900000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>3.3799999999999999</v>
+        <v>3.5800000000000001</v>
       </c>
       <c r="I8" s="0">
-        <v>58.670000000000002</v>
+        <v>59.329999999999998</v>
       </c>
       <c r="J8" s="0">
-        <v>535</v>
+        <v>393</v>
       </c>
       <c r="K8" s="0">
-        <v>6407.3999999999996</v>
+        <v>2625.96</v>
       </c>
       <c r="L8" s="0">
-        <v>64.159999999999997</v>
+        <v>52.520000000000003</v>
       </c>
       <c r="M8" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -553,40 +568,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>7422076932</v>
+        <v>4289920848</v>
       </c>
       <c r="C9" s="0">
-        <v>12829911451</v>
+        <v>7037044872</v>
       </c>
       <c r="D9" s="0">
-        <v>136619</v>
+        <v>109697</v>
       </c>
       <c r="E9" s="0">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F9" s="0">
-        <v>363951</v>
+        <v>221489</v>
       </c>
       <c r="G9" s="0">
-        <v>3.8799999999999999</v>
+        <v>3.4500000000000002</v>
       </c>
       <c r="H9" s="0">
-        <v>6.2199999999999998</v>
+        <v>5.75</v>
       </c>
       <c r="I9" s="0">
-        <v>57.850000000000001</v>
+        <v>60.960000000000001</v>
       </c>
       <c r="J9" s="0">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="K9" s="0">
-        <v>1676</v>
+        <v>2029.7</v>
       </c>
       <c r="L9" s="0">
-        <v>22.09</v>
+        <v>30.559999999999999</v>
       </c>
       <c r="M9" s="0">
-        <v>0.075999999999999998</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="10">
@@ -594,40 +609,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>1350708588</v>
+        <v>1411867519</v>
       </c>
       <c r="C10" s="0">
-        <v>2747749478</v>
+        <v>2406330815</v>
       </c>
       <c r="D10" s="0">
-        <v>234850</v>
+        <v>102923</v>
       </c>
       <c r="E10" s="0">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="F10" s="0">
-        <v>27820</v>
+        <v>45066</v>
       </c>
       <c r="G10" s="0">
-        <v>2.3799999999999999</v>
+        <v>1.9299999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>5.9199999999999999</v>
+        <v>3.3799999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>49.159999999999997</v>
+        <v>58.670000000000002</v>
       </c>
       <c r="J10" s="0">
-        <v>907</v>
+        <v>535</v>
       </c>
       <c r="K10" s="0">
-        <v>5863.6599999999999</v>
+        <v>6407.3999999999996</v>
       </c>
       <c r="L10" s="0">
-        <v>53.859999999999999</v>
+        <v>64.159999999999997</v>
       </c>
       <c r="M10" s="0">
-        <v>0.14799999999999999</v>
+        <v>0.20999999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -635,40 +650,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>8474329</v>
+        <v>7422076932</v>
       </c>
       <c r="C11" s="0">
-        <v>18604819</v>
+        <v>12829911451</v>
       </c>
       <c r="D11" s="0">
-        <v>68907</v>
+        <v>136619</v>
       </c>
       <c r="E11" s="0">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="F11" s="0">
-        <v>194</v>
+        <v>363951</v>
       </c>
       <c r="G11" s="0">
-        <v>0.71999999999999997</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>1.51</v>
+        <v>6.2199999999999998</v>
       </c>
       <c r="I11" s="0">
-        <v>45.549999999999997</v>
+        <v>57.850000000000001</v>
       </c>
       <c r="J11" s="0">
-        <v>738</v>
+        <v>464</v>
       </c>
       <c r="K11" s="0">
-        <v>4420.25</v>
+        <v>1676</v>
       </c>
       <c r="L11" s="0">
-        <v>34</v>
+        <v>22.09</v>
       </c>
       <c r="M11" s="0">
-        <v>0.097000000000000003</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -676,40 +691,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>20335362931</v>
+        <v>1350708588</v>
       </c>
       <c r="C12" s="0">
-        <v>32444868675</v>
+        <v>2747749478</v>
       </c>
       <c r="D12" s="0">
-        <v>277070</v>
+        <v>234850</v>
       </c>
       <c r="E12" s="0">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="F12" s="0">
-        <v>288958</v>
+        <v>27820</v>
       </c>
       <c r="G12" s="0">
-        <v>2.4700000000000002</v>
+        <v>2.3799999999999999</v>
       </c>
       <c r="H12" s="0">
-        <v>5.7300000000000004</v>
+        <v>5.9199999999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>62.68</v>
+        <v>49.159999999999997</v>
       </c>
       <c r="J12" s="0">
-        <v>844</v>
+        <v>907</v>
       </c>
       <c r="K12" s="0">
-        <v>5284.0299999999997</v>
+        <v>5863.6599999999999</v>
       </c>
       <c r="L12" s="0">
-        <v>39.799999999999997</v>
+        <v>53.859999999999999</v>
       </c>
       <c r="M12" s="0">
-        <v>0.109</v>
+        <v>0.14799999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -717,40 +732,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>38840353469</v>
+        <v>8474329</v>
       </c>
       <c r="C13" s="0">
-        <v>62167519813</v>
+        <v>18604819</v>
       </c>
       <c r="D13" s="0">
-        <v>357490</v>
+        <v>68907</v>
       </c>
       <c r="E13" s="0">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="F13" s="0">
-        <v>389141</v>
+        <v>194</v>
       </c>
       <c r="G13" s="0">
-        <v>2.2400000000000002</v>
+        <v>0.71999999999999997</v>
       </c>
       <c r="H13" s="0">
-        <v>5.7599999999999998</v>
+        <v>1.51</v>
       </c>
       <c r="I13" s="0">
-        <v>62.479999999999997</v>
+        <v>45.549999999999997</v>
       </c>
       <c r="J13" s="0">
-        <v>977</v>
+        <v>738</v>
       </c>
       <c r="K13" s="0">
-        <v>5300.2299999999996</v>
+        <v>4420.25</v>
       </c>
       <c r="L13" s="0">
-        <v>32.450000000000003</v>
+        <v>34</v>
       </c>
       <c r="M13" s="0">
-        <v>0.085000000000000006</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="14">
@@ -758,40 +773,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>10730245543</v>
+        <v>20335362931</v>
       </c>
       <c r="C14" s="0">
-        <v>16149429385</v>
+        <v>32444868675</v>
       </c>
       <c r="D14" s="0">
-        <v>506569</v>
+        <v>277070</v>
       </c>
       <c r="E14" s="0">
-        <v>185</v>
+        <v>133</v>
       </c>
       <c r="F14" s="0">
-        <v>84719</v>
+        <v>288958</v>
       </c>
       <c r="G14" s="0">
-        <v>2.6600000000000001</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="H14" s="0">
-        <v>7.1900000000000004</v>
+        <v>5.7300000000000004</v>
       </c>
       <c r="I14" s="0">
-        <v>66.439999999999998</v>
+        <v>62.68</v>
       </c>
       <c r="J14" s="0">
-        <v>1030</v>
+        <v>844</v>
       </c>
       <c r="K14" s="0">
-        <v>4935.4799999999996</v>
+        <v>5284.0299999999997</v>
       </c>
       <c r="L14" s="0">
-        <v>26.66</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="M14" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="15">
@@ -799,40 +814,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>47056720011</v>
+        <v>38840353469</v>
       </c>
       <c r="C15" s="0">
-        <v>75649435807</v>
+        <v>62167519813</v>
       </c>
       <c r="D15" s="0">
-        <v>518893</v>
+        <v>357490</v>
       </c>
       <c r="E15" s="0">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="F15" s="0">
-        <v>335079</v>
+        <v>389141</v>
       </c>
       <c r="G15" s="0">
-        <v>2.2999999999999998</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="H15" s="0">
-        <v>7.04</v>
+        <v>5.7599999999999998</v>
       </c>
       <c r="I15" s="0">
-        <v>62.200000000000003</v>
+        <v>62.479999999999997</v>
       </c>
       <c r="J15" s="0">
-        <v>1211</v>
+        <v>977</v>
       </c>
       <c r="K15" s="0">
-        <v>6175.2200000000003</v>
+        <v>5300.2299999999996</v>
       </c>
       <c r="L15" s="0">
-        <v>32.969999999999999</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="M15" s="0">
-        <v>0.084000000000000005</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="16">
@@ -840,40 +855,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>4515672524</v>
+        <v>10730245543</v>
       </c>
       <c r="C16" s="0">
-        <v>8060084515</v>
+        <v>16149429385</v>
       </c>
       <c r="D16" s="0">
-        <v>504386</v>
+        <v>506569</v>
       </c>
       <c r="E16" s="0">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F16" s="0">
-        <v>26025</v>
+        <v>84719</v>
       </c>
       <c r="G16" s="0">
-        <v>1.6299999999999999</v>
+        <v>2.6600000000000001</v>
       </c>
       <c r="H16" s="0">
-        <v>6.21</v>
+        <v>7.1900000000000004</v>
       </c>
       <c r="I16" s="0">
-        <v>56.030000000000001</v>
+        <v>66.439999999999998</v>
       </c>
       <c r="J16" s="0">
-        <v>1606</v>
+        <v>1030</v>
       </c>
       <c r="K16" s="0">
-        <v>7006.9300000000003</v>
+        <v>4935.4799999999996</v>
       </c>
       <c r="L16" s="0">
-        <v>36.340000000000003</v>
+        <v>26.66</v>
       </c>
       <c r="M16" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="17">
@@ -881,40 +896,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>2681705993</v>
+        <v>47056720011</v>
       </c>
       <c r="C17" s="0">
-        <v>4810620682</v>
+        <v>75649435807</v>
       </c>
       <c r="D17" s="0">
-        <v>132597</v>
+        <v>518893</v>
       </c>
       <c r="E17" s="0">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="F17" s="0">
-        <v>114493</v>
+        <v>335079</v>
       </c>
       <c r="G17" s="0">
-        <v>3.1600000000000001</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H17" s="0">
-        <v>4.1600000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="I17" s="0">
-        <v>55.75</v>
+        <v>62.200000000000003</v>
       </c>
       <c r="J17" s="0">
-        <v>378</v>
+        <v>1211</v>
       </c>
       <c r="K17" s="0">
-        <v>5609.7399999999998</v>
+        <v>6175.2200000000003</v>
       </c>
       <c r="L17" s="0">
-        <v>50.079999999999998</v>
+        <v>32.969999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.17599999999999999</v>
+        <v>0.084000000000000005</v>
       </c>
     </row>
     <row r="18">
@@ -922,40 +937,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>35489506247</v>
+        <v>4515672524</v>
       </c>
       <c r="C18" s="0">
-        <v>66891812806</v>
+        <v>8060084515</v>
       </c>
       <c r="D18" s="0">
-        <v>326079</v>
+        <v>504386</v>
       </c>
       <c r="E18" s="0">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="F18" s="0">
-        <v>686453</v>
+        <v>26025</v>
       </c>
       <c r="G18" s="0">
-        <v>3.3500000000000001</v>
+        <v>1.6299999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>6.3200000000000003</v>
+        <v>6.21</v>
       </c>
       <c r="I18" s="0">
-        <v>53.060000000000002</v>
+        <v>56.030000000000001</v>
       </c>
       <c r="J18" s="0">
-        <v>688</v>
+        <v>1606</v>
       </c>
       <c r="K18" s="0">
-        <v>4492.6300000000001</v>
+        <v>7006.9300000000003</v>
       </c>
       <c r="L18" s="0">
-        <v>31.719999999999999</v>
+        <v>36.340000000000003</v>
       </c>
       <c r="M18" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="19">
@@ -963,40 +978,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>69986524458</v>
+        <v>1100014624</v>
       </c>
       <c r="C19" s="0">
-        <v>121168904295</v>
+        <v>1732401098</v>
       </c>
       <c r="D19" s="0">
-        <v>471640</v>
+        <v>305538</v>
       </c>
       <c r="E19" s="0">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="F19" s="0">
-        <v>715601</v>
+        <v>23371</v>
       </c>
       <c r="G19" s="0">
-        <v>2.79</v>
+        <v>4.1200000000000001</v>
       </c>
       <c r="H19" s="0">
-        <v>7.21</v>
+        <v>6.6399999999999997</v>
       </c>
       <c r="I19" s="0">
-        <v>57.759999999999998</v>
+        <v>63.5</v>
       </c>
       <c r="J19" s="0">
-        <v>1002</v>
+        <v>500</v>
       </c>
       <c r="K19" s="0">
-        <v>5272.1800000000003</v>
+        <v>6312.1000000000004</v>
       </c>
       <c r="L19" s="0">
-        <v>31.210000000000001</v>
+        <v>42.560000000000002</v>
       </c>
       <c r="M19" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.13700000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1004,40 +1019,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>934888</v>
+        <v>645940891</v>
       </c>
       <c r="C20" s="0">
-        <v>1131072</v>
+        <v>911489848</v>
       </c>
       <c r="D20" s="0">
-        <v>87</v>
+        <v>218583</v>
       </c>
       <c r="E20" s="0">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="F20" s="0">
-        <v>6</v>
+        <v>9070</v>
       </c>
       <c r="G20" s="0">
-        <v>0</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="H20" s="0">
-        <v>0</v>
+        <v>4.1299999999999999</v>
       </c>
       <c r="I20" s="0">
-        <v>82.659999999999997</v>
+        <v>70.870000000000005</v>
       </c>
       <c r="J20" s="0">
-        <v>1096</v>
+        <v>638</v>
       </c>
       <c r="K20" s="0">
-        <v>4862165.9800000004</v>
+        <v>5245.8400000000001</v>
       </c>
       <c r="L20" s="0">
-        <v>28268.41</v>
+        <v>33.280000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>73.293000000000006</v>
+        <v>0.099000000000000005</v>
       </c>
     </row>
     <row r="21">
@@ -1045,40 +1060,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>1043583453</v>
+        <v>2681705993</v>
       </c>
       <c r="C21" s="0">
-        <v>1575251693</v>
+        <v>4810620682</v>
       </c>
       <c r="D21" s="0">
-        <v>365488</v>
+        <v>132597</v>
       </c>
       <c r="E21" s="0">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="F21" s="0">
-        <v>8899</v>
+        <v>114493</v>
       </c>
       <c r="G21" s="0">
-        <v>2.0600000000000001</v>
+        <v>3.1600000000000001</v>
       </c>
       <c r="H21" s="0">
-        <v>5.4900000000000002</v>
+        <v>4.1600000000000001</v>
       </c>
       <c r="I21" s="0">
-        <v>66.25</v>
+        <v>55.75</v>
       </c>
       <c r="J21" s="0">
-        <v>992</v>
+        <v>378</v>
       </c>
       <c r="K21" s="0">
-        <v>7540.5900000000001</v>
+        <v>5609.7399999999998</v>
       </c>
       <c r="L21" s="0">
-        <v>42.270000000000003</v>
+        <v>50.079999999999998</v>
       </c>
       <c r="M21" s="0">
-        <v>0.113</v>
+        <v>0.17599999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1086,40 +1101,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>32660225447</v>
+        <v>245616</v>
       </c>
       <c r="C22" s="0">
-        <v>56047238877</v>
+        <v>967500</v>
       </c>
       <c r="D22" s="0">
-        <v>462398</v>
+        <v>0</v>
       </c>
       <c r="E22" s="0">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="F22" s="0">
-        <v>244968</v>
+        <v>12</v>
       </c>
       <c r="G22" s="0">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="H22" s="0">
-        <v>6.4100000000000001</v>
+        <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>58.270000000000003</v>
+        <v>25.390000000000001</v>
       </c>
       <c r="J22" s="0">
-        <v>1278</v>
+        <v>538</v>
       </c>
       <c r="K22" s="0">
-        <v>4849.1999999999998</v>
+        <v>34010.220000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>27.09</v>
+        <v>226.72999999999999</v>
       </c>
       <c r="M22" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.78000000000000003</v>
       </c>
     </row>
     <row r="23">
@@ -1127,40 +1142,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>13157247322</v>
+        <v>35489506247</v>
       </c>
       <c r="C23" s="0">
-        <v>21851085570</v>
+        <v>66891812806</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>326079</v>
       </c>
       <c r="E23" s="0">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="F23" s="0">
-        <v>80157</v>
+        <v>686453</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>3.3500000000000001</v>
       </c>
       <c r="H23" s="0">
-        <v>0</v>
+        <v>6.3200000000000003</v>
       </c>
       <c r="I23" s="0">
-        <v>60.210000000000001</v>
+        <v>53.060000000000002</v>
       </c>
       <c r="J23" s="0">
-        <v>1484</v>
+        <v>688</v>
       </c>
       <c r="K23" s="0">
-        <v>6082.7600000000002</v>
+        <v>4492.6300000000001</v>
       </c>
       <c r="L23" s="0">
-        <v>33.060000000000002</v>
+        <v>31.719999999999999</v>
       </c>
       <c r="M23" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="24">
@@ -1168,40 +1183,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>3872373763</v>
+        <v>69986627573</v>
       </c>
       <c r="C24" s="0">
-        <v>6172407107</v>
+        <v>121170190251</v>
       </c>
       <c r="D24" s="0">
-        <v>458915</v>
+        <v>471645</v>
       </c>
       <c r="E24" s="0">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="F24" s="0">
-        <v>19128</v>
+        <v>715619</v>
       </c>
       <c r="G24" s="0">
-        <v>1.4199999999999999</v>
+        <v>2.79</v>
       </c>
       <c r="H24" s="0">
-        <v>4.7800000000000002</v>
+        <v>7.21</v>
       </c>
       <c r="I24" s="0">
-        <v>62.740000000000002</v>
+        <v>57.759999999999998</v>
       </c>
       <c r="J24" s="0">
-        <v>1380</v>
+        <v>1002</v>
       </c>
       <c r="K24" s="0">
-        <v>6560.54</v>
+        <v>5272.1099999999997</v>
       </c>
       <c r="L24" s="0">
-        <v>28.050000000000001</v>
+        <v>31.210000000000001</v>
       </c>
       <c r="M24" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="25">
@@ -1209,40 +1224,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>7556513617</v>
+        <v>934888</v>
       </c>
       <c r="C25" s="0">
-        <v>11549571538</v>
+        <v>1131072</v>
       </c>
       <c r="D25" s="0">
-        <v>361376</v>
+        <v>87</v>
       </c>
       <c r="E25" s="0">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="F25" s="0">
-        <v>20732</v>
+        <v>6</v>
       </c>
       <c r="G25" s="0">
-        <v>0.65000000000000002</v>
+        <v>0</v>
       </c>
       <c r="H25" s="0">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>65.430000000000007</v>
+        <v>82.659999999999997</v>
       </c>
       <c r="J25" s="0">
-        <v>2632</v>
+        <v>1096</v>
       </c>
       <c r="K25" s="0">
-        <v>8337.2000000000007</v>
+        <v>4862165.9800000004</v>
       </c>
       <c r="L25" s="0">
-        <v>39.380000000000003</v>
+        <v>28268.41</v>
       </c>
       <c r="M25" s="0">
-        <v>0.085999999999999993</v>
+        <v>73.293000000000006</v>
       </c>
     </row>
     <row r="26">
@@ -1250,40 +1265,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>2665252729</v>
+        <v>1043583453</v>
       </c>
       <c r="C26" s="0">
-        <v>4329066272</v>
+        <v>1575251693</v>
       </c>
       <c r="D26" s="0">
-        <v>0</v>
+        <v>365488</v>
       </c>
       <c r="E26" s="0">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="F26" s="0">
-        <v>6200</v>
+        <v>8899</v>
       </c>
       <c r="G26" s="0">
-        <v>0</v>
+        <v>2.0600000000000001</v>
       </c>
       <c r="H26" s="0">
-        <v>0</v>
+        <v>5.4900000000000002</v>
       </c>
       <c r="I26" s="0">
-        <v>61.57</v>
+        <v>66.25</v>
       </c>
       <c r="J26" s="0">
-        <v>2934</v>
+        <v>992</v>
       </c>
       <c r="K26" s="0">
-        <v>7817.4399999999996</v>
+        <v>7540.5900000000001</v>
       </c>
       <c r="L26" s="0">
-        <v>32.850000000000001</v>
+        <v>42.270000000000003</v>
       </c>
       <c r="M26" s="0">
-        <v>0.070999999999999994</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="27">
@@ -1291,40 +1306,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>4799955587</v>
+        <v>32660225447</v>
       </c>
       <c r="C27" s="0">
-        <v>7642475656</v>
+        <v>56047238877</v>
       </c>
       <c r="D27" s="0">
-        <v>557032</v>
+        <v>462398</v>
       </c>
       <c r="E27" s="0">
-        <v>254</v>
+        <v>179</v>
       </c>
       <c r="F27" s="0">
-        <v>9764</v>
+        <v>244968</v>
       </c>
       <c r="G27" s="0">
-        <v>0.70999999999999996</v>
+        <v>2.02</v>
       </c>
       <c r="H27" s="0">
-        <v>4.7199999999999998</v>
+        <v>6.4100000000000001</v>
       </c>
       <c r="I27" s="0">
-        <v>62.810000000000002</v>
+        <v>58.270000000000003</v>
       </c>
       <c r="J27" s="0">
-        <v>3086</v>
+        <v>1278</v>
       </c>
       <c r="K27" s="0">
-        <v>10698.76</v>
+        <v>4849.1999999999998</v>
       </c>
       <c r="L27" s="0">
-        <v>42.189999999999998</v>
+        <v>27.09</v>
       </c>
       <c r="M27" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="28">
@@ -1332,40 +1347,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>5094388946</v>
+        <v>13157247322</v>
       </c>
       <c r="C28" s="0">
-        <v>9550626252</v>
+        <v>21851085570</v>
       </c>
       <c r="D28" s="0">
-        <v>816293</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0">
-        <v>289</v>
+        <v>186</v>
       </c>
       <c r="F28" s="0">
-        <v>9177</v>
+        <v>80157</v>
       </c>
       <c r="G28" s="0">
-        <v>0.78000000000000003</v>
+        <v>0</v>
       </c>
       <c r="H28" s="0">
-        <v>5.9299999999999997</v>
+        <v>0</v>
       </c>
       <c r="I28" s="0">
-        <v>53.340000000000003</v>
+        <v>60.210000000000001</v>
       </c>
       <c r="J28" s="0">
-        <v>3603</v>
+        <v>1484</v>
       </c>
       <c r="K28" s="0">
-        <v>8768.4799999999996</v>
+        <v>6082.7600000000002</v>
       </c>
       <c r="L28" s="0">
-        <v>30.350000000000001</v>
+        <v>33.060000000000002</v>
       </c>
       <c r="M28" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="29">
@@ -1373,37 +1388,37 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>773571332</v>
+        <v>3872373763</v>
       </c>
       <c r="C29" s="0">
-        <v>1830084789</v>
+        <v>6172407107</v>
       </c>
       <c r="D29" s="0">
-        <v>871469</v>
+        <v>458915</v>
       </c>
       <c r="E29" s="0">
-        <v>277</v>
+        <v>234</v>
       </c>
       <c r="F29" s="0">
-        <v>1345</v>
+        <v>19128</v>
       </c>
       <c r="G29" s="0">
-        <v>0.64000000000000001</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="H29" s="0">
-        <v>6.4000000000000004</v>
+        <v>4.7800000000000002</v>
       </c>
       <c r="I29" s="0">
-        <v>42.270000000000003</v>
+        <v>62.740000000000002</v>
       </c>
       <c r="J29" s="0">
-        <v>4912</v>
+        <v>1380</v>
       </c>
       <c r="K29" s="0">
-        <v>9192.6700000000001</v>
+        <v>6560.54</v>
       </c>
       <c r="L29" s="0">
-        <v>33.189999999999998</v>
+        <v>28.050000000000001</v>
       </c>
       <c r="M29" s="0">
         <v>0.068000000000000005</v>
@@ -1414,40 +1429,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>2604399457</v>
+        <v>7556513617</v>
       </c>
       <c r="C30" s="0">
-        <v>6084918714</v>
+        <v>11549571538</v>
       </c>
       <c r="D30" s="0">
-        <v>1236772</v>
+        <v>361376</v>
       </c>
       <c r="E30" s="0">
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="F30" s="0">
-        <v>3626</v>
+        <v>20732</v>
       </c>
       <c r="G30" s="0">
-        <v>0.73999999999999999</v>
+        <v>0.65000000000000002</v>
       </c>
       <c r="H30" s="0">
-        <v>8.0500000000000007</v>
+        <v>3.75</v>
       </c>
       <c r="I30" s="0">
-        <v>42.799999999999997</v>
+        <v>65.430000000000007</v>
       </c>
       <c r="J30" s="0">
-        <v>5549</v>
+        <v>2632</v>
       </c>
       <c r="K30" s="0">
-        <v>10350.969999999999</v>
+        <v>8337.2000000000007</v>
       </c>
       <c r="L30" s="0">
-        <v>34.219999999999999</v>
+        <v>39.380000000000003</v>
       </c>
       <c r="M30" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="31">
@@ -1455,40 +1470,40 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>3315797016</v>
+        <v>2665252729</v>
       </c>
       <c r="C31" s="0">
-        <v>7317275196</v>
+        <v>4329066272</v>
       </c>
       <c r="D31" s="0">
-        <v>715276</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F31" s="0">
-        <v>9472</v>
+        <v>6200</v>
       </c>
       <c r="G31" s="0">
-        <v>0.93000000000000005</v>
+        <v>0</v>
       </c>
       <c r="H31" s="0">
-        <v>6.4400000000000004</v>
+        <v>0</v>
       </c>
       <c r="I31" s="0">
-        <v>45.310000000000002</v>
+        <v>61.57</v>
       </c>
       <c r="J31" s="0">
-        <v>3420</v>
+        <v>2934</v>
       </c>
       <c r="K31" s="0">
-        <v>12721.77</v>
+        <v>7817.4399999999996</v>
       </c>
       <c r="L31" s="0">
-        <v>56.280000000000001</v>
+        <v>32.850000000000001</v>
       </c>
       <c r="M31" s="0">
-        <v>0.115</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="32">
@@ -1496,40 +1511,40 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>7558522549</v>
+        <v>4799955587</v>
       </c>
       <c r="C32" s="0">
-        <v>15224529400</v>
+        <v>7642475656</v>
       </c>
       <c r="D32" s="0">
-        <v>880031</v>
+        <v>557032</v>
       </c>
       <c r="E32" s="0">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F32" s="0">
-        <v>12242</v>
+        <v>9764</v>
       </c>
       <c r="G32" s="0">
         <v>0.70999999999999996</v>
       </c>
       <c r="H32" s="0">
-        <v>6.75</v>
+        <v>4.7199999999999998</v>
       </c>
       <c r="I32" s="0">
-        <v>49.649999999999999</v>
+        <v>62.810000000000002</v>
       </c>
       <c r="J32" s="0">
-        <v>4832</v>
+        <v>3086</v>
       </c>
       <c r="K32" s="0">
-        <v>14359.98</v>
+        <v>10698.76</v>
       </c>
       <c r="L32" s="0">
-        <v>55.759999999999998</v>
+        <v>42.189999999999998</v>
       </c>
       <c r="M32" s="0">
-        <v>0.11</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="33">
@@ -1537,40 +1552,40 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>3066967260</v>
+        <v>5094388946</v>
       </c>
       <c r="C33" s="0">
-        <v>7734723540</v>
+        <v>9550626252</v>
       </c>
       <c r="D33" s="0">
-        <v>1670567</v>
+        <v>816293</v>
       </c>
       <c r="E33" s="0">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="F33" s="0">
-        <v>6484</v>
+        <v>9177</v>
       </c>
       <c r="G33" s="0">
-        <v>1.3999999999999999</v>
+        <v>0.78000000000000003</v>
       </c>
       <c r="H33" s="0">
-        <v>10.49</v>
+        <v>5.9299999999999997</v>
       </c>
       <c r="I33" s="0">
-        <v>39.649999999999999</v>
+        <v>53.340000000000003</v>
       </c>
       <c r="J33" s="0">
-        <v>3751</v>
+        <v>3603</v>
       </c>
       <c r="K33" s="0">
-        <v>8718.8600000000006</v>
+        <v>8768.4799999999996</v>
       </c>
       <c r="L33" s="0">
-        <v>27.420000000000002</v>
+        <v>30.350000000000001</v>
       </c>
       <c r="M33" s="0">
-        <v>0.055</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1578,40 +1593,40 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>14259736782</v>
+        <v>773571332</v>
       </c>
       <c r="C34" s="0">
-        <v>22303477341</v>
+        <v>1830084789</v>
       </c>
       <c r="D34" s="0">
-        <v>550160</v>
+        <v>871469</v>
       </c>
       <c r="E34" s="0">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="F34" s="0">
-        <v>22799</v>
+        <v>1345</v>
       </c>
       <c r="G34" s="0">
-        <v>0.56000000000000005</v>
+        <v>0.64000000000000001</v>
       </c>
       <c r="H34" s="0">
-        <v>3.9199999999999999</v>
+        <v>6.4000000000000004</v>
       </c>
       <c r="I34" s="0">
-        <v>63.939999999999998</v>
+        <v>42.270000000000003</v>
       </c>
       <c r="J34" s="0">
-        <v>3366</v>
+        <v>4912</v>
       </c>
       <c r="K34" s="0">
-        <v>13874.34</v>
+        <v>9192.6700000000001</v>
       </c>
       <c r="L34" s="0">
-        <v>47.590000000000003</v>
+        <v>33.189999999999998</v>
       </c>
       <c r="M34" s="0">
-        <v>0.099000000000000005</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="35">
@@ -1619,40 +1634,40 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>6517876044</v>
+        <v>2604399457</v>
       </c>
       <c r="C35" s="0">
-        <v>11724723131</v>
+        <v>6084918714</v>
       </c>
       <c r="D35" s="0">
-        <v>934241</v>
+        <v>1236772</v>
       </c>
       <c r="E35" s="0">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F35" s="0">
-        <v>7956</v>
+        <v>3626</v>
       </c>
       <c r="G35" s="0">
-        <v>0.63</v>
+        <v>0.73999999999999999</v>
       </c>
       <c r="H35" s="0">
-        <v>6</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="I35" s="0">
-        <v>55.590000000000003</v>
+        <v>42.799999999999997</v>
       </c>
       <c r="J35" s="0">
-        <v>4744</v>
+        <v>5549</v>
       </c>
       <c r="K35" s="0">
-        <v>20396.029999999999</v>
+        <v>10350.969999999999</v>
       </c>
       <c r="L35" s="0">
-        <v>65.739999999999995</v>
+        <v>34.219999999999999</v>
       </c>
       <c r="M35" s="0">
-        <v>0.13100000000000001</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="36">
@@ -1660,39 +1675,244 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>375183124315</v>
+        <v>3315797016</v>
       </c>
       <c r="C36" s="0">
-        <v>641154635400</v>
+        <v>7317275196</v>
       </c>
       <c r="D36" s="0">
+        <v>715276</v>
+      </c>
+      <c r="E36" s="0">
+        <v>229</v>
+      </c>
+      <c r="F36" s="0">
+        <v>9472</v>
+      </c>
+      <c r="G36" s="0">
+        <v>0.93000000000000005</v>
+      </c>
+      <c r="H36" s="0">
+        <v>6.4400000000000004</v>
+      </c>
+      <c r="I36" s="0">
+        <v>45.310000000000002</v>
+      </c>
+      <c r="J36" s="0">
+        <v>3420</v>
+      </c>
+      <c r="K36" s="0">
+        <v>12721.77</v>
+      </c>
+      <c r="L36" s="0">
+        <v>56.280000000000001</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
+        <v>7558522549</v>
+      </c>
+      <c r="C37" s="0">
+        <v>15224529400</v>
+      </c>
+      <c r="D37" s="0">
+        <v>880031</v>
+      </c>
+      <c r="E37" s="0">
+        <v>261</v>
+      </c>
+      <c r="F37" s="0">
+        <v>12242</v>
+      </c>
+      <c r="G37" s="0">
+        <v>0.70999999999999996</v>
+      </c>
+      <c r="H37" s="0">
+        <v>6.75</v>
+      </c>
+      <c r="I37" s="0">
+        <v>49.649999999999999</v>
+      </c>
+      <c r="J37" s="0">
+        <v>4832</v>
+      </c>
+      <c r="K37" s="0">
+        <v>14359.98</v>
+      </c>
+      <c r="L37" s="0">
+        <v>55.759999999999998</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="0">
+        <v>3066967260</v>
+      </c>
+      <c r="C38" s="0">
+        <v>7734723540</v>
+      </c>
+      <c r="D38" s="0">
+        <v>1670567</v>
+      </c>
+      <c r="E38" s="0">
+        <v>318</v>
+      </c>
+      <c r="F38" s="0">
+        <v>6484</v>
+      </c>
+      <c r="G38" s="0">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="H38" s="0">
+        <v>10.49</v>
+      </c>
+      <c r="I38" s="0">
+        <v>39.649999999999999</v>
+      </c>
+      <c r="J38" s="0">
+        <v>3751</v>
+      </c>
+      <c r="K38" s="0">
+        <v>8718.8600000000006</v>
+      </c>
+      <c r="L38" s="0">
+        <v>27.420000000000002</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="0">
+        <v>14259736782</v>
+      </c>
+      <c r="C39" s="0">
+        <v>22303477341</v>
+      </c>
+      <c r="D39" s="0">
+        <v>550160</v>
+      </c>
+      <c r="E39" s="0">
+        <v>301</v>
+      </c>
+      <c r="F39" s="0">
+        <v>22799</v>
+      </c>
+      <c r="G39" s="0">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H39" s="0">
+        <v>3.9199999999999999</v>
+      </c>
+      <c r="I39" s="0">
+        <v>63.939999999999998</v>
+      </c>
+      <c r="J39" s="0">
+        <v>3366</v>
+      </c>
+      <c r="K39" s="0">
+        <v>13874.34</v>
+      </c>
+      <c r="L39" s="0">
+        <v>47.590000000000003</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0.099000000000000005</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="0">
+        <v>6517876044</v>
+      </c>
+      <c r="C40" s="0">
+        <v>11724723131</v>
+      </c>
+      <c r="D40" s="0">
+        <v>934241</v>
+      </c>
+      <c r="E40" s="0">
+        <v>306</v>
+      </c>
+      <c r="F40" s="0">
+        <v>7956</v>
+      </c>
+      <c r="G40" s="0">
+        <v>0.63</v>
+      </c>
+      <c r="H40" s="0">
+        <v>6</v>
+      </c>
+      <c r="I40" s="0">
+        <v>55.590000000000003</v>
+      </c>
+      <c r="J40" s="0">
+        <v>4744</v>
+      </c>
+      <c r="K40" s="0">
+        <v>20396.029999999999</v>
+      </c>
+      <c r="L40" s="0">
+        <v>65.739999999999995</v>
+      </c>
+      <c r="M40" s="0">
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="0">
+        <v>377832386989</v>
+      </c>
+      <c r="C41" s="0">
+        <v>645433587063</v>
+      </c>
+      <c r="D41" s="0">
         <v>0</v>
       </c>
-      <c r="E36" s="0">
-        <v>130</v>
-      </c>
-      <c r="F36" s="0">
-        <v>4876531</v>
-      </c>
-      <c r="G36" s="0">
+      <c r="E41" s="0">
+        <v>129</v>
+      </c>
+      <c r="F41" s="0">
+        <v>5000083</v>
+      </c>
+      <c r="G41" s="0">
         <v>0</v>
       </c>
-      <c r="H36" s="0">
+      <c r="H41" s="0">
         <v>0</v>
       </c>
-      <c r="I36" s="0">
-        <v>58.520000000000003</v>
-      </c>
-      <c r="J36" s="0">
-        <v>849</v>
-      </c>
-      <c r="K36" s="0">
-        <v>4920.4300000000003</v>
-      </c>
-      <c r="L36" s="0">
-        <v>33.520000000000003</v>
-      </c>
-      <c r="M36" s="0">
+      <c r="I41" s="0">
+        <v>58.539999999999999</v>
+      </c>
+      <c r="J41" s="0">
+        <v>837</v>
+      </c>
+      <c r="K41" s="0">
+        <v>4895.54</v>
+      </c>
+      <c r="L41" s="0">
+        <v>33.549999999999997</v>
+      </c>
+      <c r="M41" s="0">
         <v>0.086999999999999994</v>
       </c>
     </row>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Aircraft_Cumulative_Statistics_2020.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Aircraft_Cumulative_Statistics_2020.xlsx
@@ -13,41 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42" uniqueCount="42">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>E140</t>
-  </si>
-  <si>
-    <t>E145</t>
-  </si>
-  <si>
-    <t>CRJ-200</t>
-  </si>
-  <si>
-    <t>E170</t>
-  </si>
-  <si>
-    <t>E175</t>
-  </si>
-  <si>
-    <t>Q400</t>
-  </si>
-  <si>
-    <t>CRJ-550</t>
-  </si>
-  <si>
-    <t>CRJ-700</t>
-  </si>
-  <si>
     <t>E190</t>
   </si>
   <si>
-    <t>CRJ-900</t>
-  </si>
-  <si>
     <t>A220-100</t>
   </si>
   <si>
@@ -60,9 +33,6 @@
     <t>A320</t>
   </si>
   <si>
-    <t>A320NEO</t>
-  </si>
-  <si>
     <t>A321</t>
   </si>
   <si>
@@ -76,9 +46,6 @@
   </si>
   <si>
     <t>B717-200</t>
-  </si>
-  <si>
-    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -217,7 +184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -240,40 +207,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2">
@@ -281,40 +248,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>382980390</v>
+        <v>175524702</v>
       </c>
       <c r="C2" s="0">
-        <v>609744433</v>
+        <v>276723315</v>
       </c>
       <c r="D2" s="0">
-        <v>24091</v>
+        <v>203473</v>
       </c>
       <c r="E2" s="0">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="F2" s="0">
-        <v>40693</v>
+        <v>6734</v>
       </c>
       <c r="G2" s="0">
-        <v>1.6100000000000001</v>
+        <v>4.9500000000000002</v>
       </c>
       <c r="H2" s="0">
-        <v>2.29</v>
+        <v>7.9299999999999997</v>
       </c>
       <c r="I2" s="0">
-        <v>62.810000000000002</v>
+        <v>63.43</v>
       </c>
       <c r="J2" s="0">
-        <v>341</v>
+        <v>415</v>
       </c>
       <c r="K2" s="0">
-        <v>1756.73</v>
+        <v>2569.3600000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>39.93</v>
+        <v>25.949999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>0.16700000000000001</v>
+        <v>0.10000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -322,40 +289,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>1844326772</v>
+        <v>1350708588</v>
       </c>
       <c r="C3" s="0">
-        <v>3000070718</v>
+        <v>2747749478</v>
       </c>
       <c r="D3" s="0">
-        <v>62100</v>
+        <v>234850</v>
       </c>
       <c r="E3" s="0">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="F3" s="0">
-        <v>176750</v>
+        <v>27820</v>
       </c>
       <c r="G3" s="0">
-        <v>3.6600000000000001</v>
+        <v>2.3799999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>5.25</v>
+        <v>5.9199999999999999</v>
       </c>
       <c r="I3" s="0">
-        <v>61.479999999999997</v>
+        <v>49.159999999999997</v>
       </c>
       <c r="J3" s="0">
-        <v>339</v>
+        <v>907</v>
       </c>
       <c r="K3" s="0">
-        <v>872.95000000000005</v>
+        <v>5863.6599999999999</v>
       </c>
       <c r="L3" s="0">
-        <v>17.460000000000001</v>
+        <v>53.859999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>0.073999999999999996</v>
+        <v>0.14799999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -363,40 +330,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>2480522085</v>
+        <v>8474329</v>
       </c>
       <c r="C4" s="0">
-        <v>4610881396</v>
+        <v>18604819</v>
       </c>
       <c r="D4" s="0">
-        <v>54425</v>
+        <v>68907</v>
       </c>
       <c r="E4" s="0">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F4" s="0">
-        <v>260247</v>
+        <v>194</v>
       </c>
       <c r="G4" s="0">
-        <v>3.0699999999999998</v>
+        <v>0.71999999999999997</v>
       </c>
       <c r="H4" s="0">
-        <v>4.1699999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="I4" s="0">
-        <v>53.799999999999997</v>
+        <v>45.549999999999997</v>
       </c>
       <c r="J4" s="0">
-        <v>354</v>
+        <v>738</v>
       </c>
       <c r="K4" s="0">
-        <v>2450.5100000000002</v>
+        <v>4420.25</v>
       </c>
       <c r="L4" s="0">
-        <v>49.009999999999998</v>
+        <v>34</v>
       </c>
       <c r="M4" s="0">
-        <v>0.188</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="5">
@@ -404,40 +371,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>1184760768</v>
+        <v>15499340737</v>
       </c>
       <c r="C5" s="0">
-        <v>1960396207</v>
+        <v>24965810356</v>
       </c>
       <c r="D5" s="0">
-        <v>89271</v>
+        <v>268017</v>
       </c>
       <c r="E5" s="0">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="F5" s="0">
-        <v>49199</v>
+        <v>235530</v>
       </c>
       <c r="G5" s="0">
-        <v>2.2400000000000002</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H5" s="0">
-        <v>4.2800000000000002</v>
+        <v>5.8200000000000003</v>
       </c>
       <c r="I5" s="0">
-        <v>60.43</v>
+        <v>62.079999999999998</v>
       </c>
       <c r="J5" s="0">
-        <v>571</v>
+        <v>826</v>
       </c>
       <c r="K5" s="0">
-        <v>1892.1099999999999</v>
+        <v>5477.0900000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>27.109999999999999</v>
+        <v>42.670000000000002</v>
       </c>
       <c r="M5" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.11899999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -445,40 +412,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>16227196611</v>
+        <v>11545667203</v>
       </c>
       <c r="C6" s="0">
-        <v>27622220218</v>
+        <v>18311036448</v>
       </c>
       <c r="D6" s="0">
-        <v>135983</v>
+        <v>280887</v>
       </c>
       <c r="E6" s="0">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="F6" s="0">
-        <v>595842</v>
+        <v>140738</v>
       </c>
       <c r="G6" s="0">
-        <v>2.9300000000000002</v>
+        <v>2.1600000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>5.6600000000000001</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I6" s="0">
-        <v>58.75</v>
+        <v>63.049999999999997</v>
       </c>
       <c r="J6" s="0">
-        <v>619</v>
+        <v>856</v>
       </c>
       <c r="K6" s="0">
-        <v>1788.53</v>
+        <v>5561.2700000000004</v>
       </c>
       <c r="L6" s="0">
-        <v>23.870000000000001</v>
+        <v>36.609999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.073999999999999996</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -486,40 +453,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>519978038</v>
+        <v>32031037187</v>
       </c>
       <c r="C7" s="0">
-        <v>1023062828</v>
+        <v>51364402622</v>
       </c>
       <c r="D7" s="0">
-        <v>95524</v>
+        <v>494174</v>
       </c>
       <c r="E7" s="0">
-        <v>76</v>
+        <v>184</v>
       </c>
       <c r="F7" s="0">
-        <v>50388</v>
+        <v>248669</v>
       </c>
       <c r="G7" s="0">
-        <v>4.7000000000000002</v>
+        <v>2.3900000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>5.6100000000000003</v>
+        <v>6.96</v>
       </c>
       <c r="I7" s="0">
-        <v>50.829999999999998</v>
+        <v>62.359999999999999</v>
       </c>
       <c r="J7" s="0">
-        <v>267</v>
+        <v>1132</v>
       </c>
       <c r="K7" s="0">
-        <v>2250.02</v>
+        <v>6944.5100000000002</v>
       </c>
       <c r="L7" s="0">
-        <v>29.609999999999999</v>
+        <v>37.979999999999997</v>
       </c>
       <c r="M7" s="0">
-        <v>0.13200000000000001</v>
+        <v>0.098000000000000004</v>
       </c>
     </row>
     <row r="8">
@@ -527,40 +494,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>379832495</v>
+        <v>2024901315</v>
       </c>
       <c r="C8" s="0">
-        <v>640163300</v>
+        <v>3318175586</v>
       </c>
       <c r="D8" s="0">
-        <v>47036</v>
+        <v>539541</v>
       </c>
       <c r="E8" s="0">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="F8" s="0">
-        <v>32549</v>
+        <v>11233</v>
       </c>
       <c r="G8" s="0">
-        <v>2.3900000000000001</v>
+        <v>1.8300000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>3.5800000000000001</v>
+        <v>6.5800000000000001</v>
       </c>
       <c r="I8" s="0">
-        <v>59.329999999999998</v>
+        <v>61.020000000000003</v>
       </c>
       <c r="J8" s="0">
-        <v>393</v>
+        <v>1507</v>
       </c>
       <c r="K8" s="0">
-        <v>2625.96</v>
+        <v>9152.4300000000003</v>
       </c>
       <c r="L8" s="0">
-        <v>52.520000000000003</v>
+        <v>46.700000000000003</v>
       </c>
       <c r="M8" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="9">
@@ -568,40 +535,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>4289920848</v>
+        <v>1100014624</v>
       </c>
       <c r="C9" s="0">
-        <v>7037044872</v>
+        <v>1732401098</v>
       </c>
       <c r="D9" s="0">
-        <v>109697</v>
+        <v>305538</v>
       </c>
       <c r="E9" s="0">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="F9" s="0">
-        <v>221489</v>
+        <v>23371</v>
       </c>
       <c r="G9" s="0">
-        <v>3.4500000000000002</v>
+        <v>4.1200000000000001</v>
       </c>
       <c r="H9" s="0">
-        <v>5.75</v>
+        <v>6.6399999999999997</v>
       </c>
       <c r="I9" s="0">
-        <v>60.960000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="J9" s="0">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="K9" s="0">
-        <v>2029.7</v>
+        <v>6312.1000000000004</v>
       </c>
       <c r="L9" s="0">
-        <v>30.559999999999999</v>
+        <v>42.560000000000002</v>
       </c>
       <c r="M9" s="0">
-        <v>0.106</v>
+        <v>0.13700000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -609,40 +576,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>1411867519</v>
+        <v>645940891</v>
       </c>
       <c r="C10" s="0">
-        <v>2406330815</v>
+        <v>911489848</v>
       </c>
       <c r="D10" s="0">
-        <v>102923</v>
+        <v>218583</v>
       </c>
       <c r="E10" s="0">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="F10" s="0">
-        <v>45066</v>
+        <v>9070</v>
       </c>
       <c r="G10" s="0">
-        <v>1.9299999999999999</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>3.3799999999999999</v>
+        <v>4.1299999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>58.670000000000002</v>
+        <v>70.870000000000005</v>
       </c>
       <c r="J10" s="0">
-        <v>535</v>
+        <v>638</v>
       </c>
       <c r="K10" s="0">
-        <v>6407.3999999999996</v>
+        <v>5245.8400000000001</v>
       </c>
       <c r="L10" s="0">
-        <v>64.159999999999997</v>
+        <v>33.280000000000001</v>
       </c>
       <c r="M10" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.099000000000000005</v>
       </c>
     </row>
     <row r="11">
@@ -650,40 +617,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>7422076932</v>
+        <v>2437612916</v>
       </c>
       <c r="C11" s="0">
-        <v>12829911451</v>
+        <v>4310256394</v>
       </c>
       <c r="D11" s="0">
-        <v>136619</v>
+        <v>147510</v>
       </c>
       <c r="E11" s="0">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="F11" s="0">
-        <v>363951</v>
+        <v>86981</v>
       </c>
       <c r="G11" s="0">
-        <v>3.8799999999999999</v>
+        <v>2.98</v>
       </c>
       <c r="H11" s="0">
-        <v>6.2199999999999998</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="I11" s="0">
-        <v>57.850000000000001</v>
+        <v>56.549999999999997</v>
       </c>
       <c r="J11" s="0">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="K11" s="0">
-        <v>1676</v>
+        <v>5497.2399999999998</v>
       </c>
       <c r="L11" s="0">
-        <v>22.09</v>
+        <v>50.170000000000002</v>
       </c>
       <c r="M11" s="0">
-        <v>0.075999999999999998</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -691,40 +658,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>1350708588</v>
+        <v>2418175248</v>
       </c>
       <c r="C12" s="0">
-        <v>2747749478</v>
+        <v>3786967567</v>
       </c>
       <c r="D12" s="0">
-        <v>234850</v>
+        <v>197753</v>
       </c>
       <c r="E12" s="0">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="F12" s="0">
-        <v>27820</v>
+        <v>28790</v>
       </c>
       <c r="G12" s="0">
-        <v>2.3799999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="H12" s="0">
-        <v>5.9199999999999999</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="I12" s="0">
-        <v>49.159999999999997</v>
+        <v>63.859999999999999</v>
       </c>
       <c r="J12" s="0">
-        <v>907</v>
+        <v>1047</v>
       </c>
       <c r="K12" s="0">
-        <v>5863.6599999999999</v>
+        <v>6011.6300000000001</v>
       </c>
       <c r="L12" s="0">
-        <v>53.859999999999999</v>
+        <v>47.850000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.14799999999999999</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="13">
@@ -732,40 +699,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>8474329</v>
+        <v>40203483815</v>
       </c>
       <c r="C13" s="0">
-        <v>18604819</v>
+        <v>63913256396</v>
       </c>
       <c r="D13" s="0">
-        <v>68907</v>
+        <v>406625</v>
       </c>
       <c r="E13" s="0">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="F13" s="0">
-        <v>194</v>
+        <v>371587</v>
       </c>
       <c r="G13" s="0">
-        <v>0.71999999999999997</v>
+        <v>2.3599999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>1.51</v>
+        <v>6.4699999999999998</v>
       </c>
       <c r="I13" s="0">
-        <v>45.549999999999997</v>
+        <v>62.899999999999999</v>
       </c>
       <c r="J13" s="0">
-        <v>738</v>
+        <v>1042</v>
       </c>
       <c r="K13" s="0">
-        <v>4420.25</v>
+        <v>6319.3299999999999</v>
       </c>
       <c r="L13" s="0">
-        <v>34</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="M13" s="0">
-        <v>0.097000000000000003</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -773,40 +740,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>20335362931</v>
+        <v>934888</v>
       </c>
       <c r="C14" s="0">
-        <v>32444868675</v>
+        <v>1131072</v>
       </c>
       <c r="D14" s="0">
-        <v>277070</v>
+        <v>1984</v>
       </c>
       <c r="E14" s="0">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="F14" s="0">
-        <v>288958</v>
+        <v>6</v>
       </c>
       <c r="G14" s="0">
-        <v>2.4700000000000002</v>
+        <v>0.01</v>
       </c>
       <c r="H14" s="0">
-        <v>5.7300000000000004</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="I14" s="0">
-        <v>62.68</v>
+        <v>82.659999999999997</v>
       </c>
       <c r="J14" s="0">
-        <v>844</v>
+        <v>1096</v>
       </c>
       <c r="K14" s="0">
-        <v>5284.0299999999997</v>
+        <v>16946.040000000001</v>
       </c>
       <c r="L14" s="0">
-        <v>39.799999999999997</v>
+        <v>98.519999999999996</v>
       </c>
       <c r="M14" s="0">
-        <v>0.109</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="15">
@@ -814,40 +781,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>38840353469</v>
+        <v>457755315</v>
       </c>
       <c r="C15" s="0">
-        <v>62167519813</v>
+        <v>611546877</v>
       </c>
       <c r="D15" s="0">
-        <v>357490</v>
+        <v>280526</v>
       </c>
       <c r="E15" s="0">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F15" s="0">
-        <v>389141</v>
+        <v>3517</v>
       </c>
       <c r="G15" s="0">
-        <v>2.2400000000000002</v>
+        <v>1.6100000000000001</v>
       </c>
       <c r="H15" s="0">
-        <v>5.7599999999999998</v>
+        <v>4.21</v>
       </c>
       <c r="I15" s="0">
-        <v>62.479999999999997</v>
+        <v>74.849999999999994</v>
       </c>
       <c r="J15" s="0">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="K15" s="0">
-        <v>5300.2299999999996</v>
+        <v>11439.440000000001</v>
       </c>
       <c r="L15" s="0">
-        <v>32.450000000000003</v>
+        <v>63.909999999999997</v>
       </c>
       <c r="M15" s="0">
-        <v>0.085000000000000006</v>
+        <v>0.17199999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -855,40 +822,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>10730245543</v>
+        <v>23862180855</v>
       </c>
       <c r="C16" s="0">
-        <v>16149429385</v>
+        <v>39760931297</v>
       </c>
       <c r="D16" s="0">
-        <v>506569</v>
+        <v>411646</v>
       </c>
       <c r="E16" s="0">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F16" s="0">
-        <v>84719</v>
+        <v>183554</v>
       </c>
       <c r="G16" s="0">
-        <v>2.6600000000000001</v>
+        <v>1.8999999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>7.1900000000000004</v>
+        <v>5.7400000000000002</v>
       </c>
       <c r="I16" s="0">
-        <v>66.439999999999998</v>
+        <v>60.009999999999998</v>
       </c>
       <c r="J16" s="0">
-        <v>1030</v>
+        <v>1207</v>
       </c>
       <c r="K16" s="0">
-        <v>4935.4799999999996</v>
+        <v>5368.0299999999997</v>
       </c>
       <c r="L16" s="0">
-        <v>26.66</v>
+        <v>29.920000000000002</v>
       </c>
       <c r="M16" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="17">
@@ -896,40 +863,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>47056720011</v>
+        <v>13157247322</v>
       </c>
       <c r="C17" s="0">
-        <v>75649435807</v>
+        <v>21851085570</v>
       </c>
       <c r="D17" s="0">
-        <v>518893</v>
+        <v>387637</v>
       </c>
       <c r="E17" s="0">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F17" s="0">
-        <v>335079</v>
+        <v>80157</v>
       </c>
       <c r="G17" s="0">
-        <v>2.2999999999999998</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="H17" s="0">
-        <v>7.04</v>
+        <v>5.0800000000000001</v>
       </c>
       <c r="I17" s="0">
-        <v>62.200000000000003</v>
+        <v>60.210000000000001</v>
       </c>
       <c r="J17" s="0">
-        <v>1211</v>
+        <v>1484</v>
       </c>
       <c r="K17" s="0">
-        <v>6175.2200000000003</v>
+        <v>6082.7600000000002</v>
       </c>
       <c r="L17" s="0">
-        <v>32.969999999999999</v>
+        <v>33.060000000000002</v>
       </c>
       <c r="M17" s="0">
-        <v>0.084000000000000005</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="18">
@@ -937,40 +904,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>4515672524</v>
+        <v>3872373763</v>
       </c>
       <c r="C18" s="0">
-        <v>8060084515</v>
+        <v>6172407107</v>
       </c>
       <c r="D18" s="0">
-        <v>504386</v>
+        <v>458915</v>
       </c>
       <c r="E18" s="0">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="F18" s="0">
-        <v>26025</v>
+        <v>19128</v>
       </c>
       <c r="G18" s="0">
-        <v>1.6299999999999999</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>6.21</v>
+        <v>4.7800000000000002</v>
       </c>
       <c r="I18" s="0">
-        <v>56.030000000000001</v>
+        <v>62.740000000000002</v>
       </c>
       <c r="J18" s="0">
-        <v>1606</v>
+        <v>1380</v>
       </c>
       <c r="K18" s="0">
-        <v>7006.9300000000003</v>
+        <v>6560.54</v>
       </c>
       <c r="L18" s="0">
-        <v>36.340000000000003</v>
+        <v>28.050000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="19">
@@ -978,40 +945,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>1100014624</v>
+        <v>7556513617</v>
       </c>
       <c r="C19" s="0">
-        <v>1732401098</v>
+        <v>11549571538</v>
       </c>
       <c r="D19" s="0">
-        <v>305538</v>
+        <v>361376</v>
       </c>
       <c r="E19" s="0">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="F19" s="0">
-        <v>23371</v>
+        <v>20732</v>
       </c>
       <c r="G19" s="0">
-        <v>4.1200000000000001</v>
+        <v>0.65000000000000002</v>
       </c>
       <c r="H19" s="0">
-        <v>6.6399999999999997</v>
+        <v>3.75</v>
       </c>
       <c r="I19" s="0">
-        <v>63.5</v>
+        <v>65.430000000000007</v>
       </c>
       <c r="J19" s="0">
-        <v>500</v>
+        <v>2632</v>
       </c>
       <c r="K19" s="0">
-        <v>6312.1000000000004</v>
+        <v>8330.7999999999993</v>
       </c>
       <c r="L19" s="0">
-        <v>42.560000000000002</v>
+        <v>39.350000000000001</v>
       </c>
       <c r="M19" s="0">
-        <v>0.13700000000000001</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="20">
@@ -1019,40 +986,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>645940891</v>
+        <v>2665252729</v>
       </c>
       <c r="C20" s="0">
-        <v>911489848</v>
+        <v>4329066272</v>
       </c>
       <c r="D20" s="0">
-        <v>218583</v>
+        <v>413079</v>
       </c>
       <c r="E20" s="0">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="F20" s="0">
-        <v>9070</v>
+        <v>6200</v>
       </c>
       <c r="G20" s="0">
-        <v>2.1800000000000002</v>
+        <v>0.58999999999999997</v>
       </c>
       <c r="H20" s="0">
-        <v>4.1299999999999999</v>
+        <v>3.73</v>
       </c>
       <c r="I20" s="0">
-        <v>70.870000000000005</v>
+        <v>61.57</v>
       </c>
       <c r="J20" s="0">
-        <v>638</v>
+        <v>2934</v>
       </c>
       <c r="K20" s="0">
-        <v>5245.8400000000001</v>
+        <v>7817.4399999999996</v>
       </c>
       <c r="L20" s="0">
-        <v>33.280000000000001</v>
+        <v>32.850000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.099000000000000005</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="21">
@@ -1060,40 +1027,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>2681705993</v>
+        <v>1571675225</v>
       </c>
       <c r="C21" s="0">
-        <v>4810620682</v>
+        <v>2475280760</v>
       </c>
       <c r="D21" s="0">
-        <v>132597</v>
+        <v>499049</v>
       </c>
       <c r="E21" s="0">
-        <v>114</v>
+        <v>240</v>
       </c>
       <c r="F21" s="0">
-        <v>114493</v>
+        <v>3331</v>
       </c>
       <c r="G21" s="0">
-        <v>3.1600000000000001</v>
+        <v>0.67000000000000004</v>
       </c>
       <c r="H21" s="0">
-        <v>4.1600000000000001</v>
+        <v>4.54</v>
       </c>
       <c r="I21" s="0">
-        <v>55.75</v>
+        <v>63.490000000000002</v>
       </c>
       <c r="J21" s="0">
-        <v>378</v>
+        <v>3131</v>
       </c>
       <c r="K21" s="0">
-        <v>5609.7399999999998</v>
+        <v>8882.5799999999999</v>
       </c>
       <c r="L21" s="0">
-        <v>50.079999999999998</v>
+        <v>37.369999999999997</v>
       </c>
       <c r="M21" s="0">
-        <v>0.17599999999999999</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="22">
@@ -1101,40 +1068,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>245616</v>
+        <v>5094388946</v>
       </c>
       <c r="C22" s="0">
-        <v>967500</v>
+        <v>9550626252</v>
       </c>
       <c r="D22" s="0">
-        <v>0</v>
+        <v>816293</v>
       </c>
       <c r="E22" s="0">
-        <v>150</v>
+        <v>289</v>
       </c>
       <c r="F22" s="0">
-        <v>12</v>
+        <v>9177</v>
       </c>
       <c r="G22" s="0">
-        <v>0</v>
+        <v>0.78000000000000003</v>
       </c>
       <c r="H22" s="0">
-        <v>0</v>
+        <v>5.9299999999999997</v>
       </c>
       <c r="I22" s="0">
-        <v>25.390000000000001</v>
+        <v>53.340000000000003</v>
       </c>
       <c r="J22" s="0">
-        <v>538</v>
+        <v>3603</v>
       </c>
       <c r="K22" s="0">
-        <v>34010.220000000001</v>
+        <v>8768.4799999999996</v>
       </c>
       <c r="L22" s="0">
-        <v>226.72999999999999</v>
+        <v>30.350000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.78000000000000003</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1142,40 +1109,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>35489506247</v>
+        <v>773571332</v>
       </c>
       <c r="C23" s="0">
-        <v>66891812806</v>
+        <v>1830084789</v>
       </c>
       <c r="D23" s="0">
-        <v>326079</v>
+        <v>871469</v>
       </c>
       <c r="E23" s="0">
-        <v>142</v>
+        <v>277</v>
       </c>
       <c r="F23" s="0">
-        <v>686453</v>
+        <v>1345</v>
       </c>
       <c r="G23" s="0">
-        <v>3.3500000000000001</v>
+        <v>0.64000000000000001</v>
       </c>
       <c r="H23" s="0">
-        <v>6.3200000000000003</v>
+        <v>6.4000000000000004</v>
       </c>
       <c r="I23" s="0">
-        <v>53.060000000000002</v>
+        <v>42.270000000000003</v>
       </c>
       <c r="J23" s="0">
-        <v>688</v>
+        <v>4912</v>
       </c>
       <c r="K23" s="0">
-        <v>4492.6300000000001</v>
+        <v>9192.6700000000001</v>
       </c>
       <c r="L23" s="0">
-        <v>31.719999999999999</v>
+        <v>33.189999999999998</v>
       </c>
       <c r="M23" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="24">
@@ -1183,40 +1150,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>69986627573</v>
+        <v>2604399457</v>
       </c>
       <c r="C24" s="0">
-        <v>121170190251</v>
+        <v>6084918714</v>
       </c>
       <c r="D24" s="0">
-        <v>471645</v>
+        <v>1236772</v>
       </c>
       <c r="E24" s="0">
-        <v>169</v>
+        <v>302</v>
       </c>
       <c r="F24" s="0">
-        <v>715619</v>
+        <v>3626</v>
       </c>
       <c r="G24" s="0">
-        <v>2.79</v>
+        <v>0.73999999999999999</v>
       </c>
       <c r="H24" s="0">
-        <v>7.21</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="I24" s="0">
-        <v>57.759999999999998</v>
+        <v>42.799999999999997</v>
       </c>
       <c r="J24" s="0">
-        <v>1002</v>
+        <v>5549</v>
       </c>
       <c r="K24" s="0">
-        <v>5272.1099999999997</v>
+        <v>10350.969999999999</v>
       </c>
       <c r="L24" s="0">
-        <v>31.210000000000001</v>
+        <v>34.219999999999999</v>
       </c>
       <c r="M24" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="25">
@@ -1224,40 +1191,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>934888</v>
+        <v>3315797016</v>
       </c>
       <c r="C25" s="0">
-        <v>1131072</v>
+        <v>7317275196</v>
       </c>
       <c r="D25" s="0">
-        <v>87</v>
+        <v>715276</v>
       </c>
       <c r="E25" s="0">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="F25" s="0">
-        <v>6</v>
+        <v>9472</v>
       </c>
       <c r="G25" s="0">
-        <v>0</v>
+        <v>0.93000000000000005</v>
       </c>
       <c r="H25" s="0">
-        <v>0</v>
+        <v>6.4400000000000004</v>
       </c>
       <c r="I25" s="0">
-        <v>82.659999999999997</v>
+        <v>45.310000000000002</v>
       </c>
       <c r="J25" s="0">
-        <v>1096</v>
+        <v>3420</v>
       </c>
       <c r="K25" s="0">
-        <v>4862165.9800000004</v>
+        <v>12721.77</v>
       </c>
       <c r="L25" s="0">
-        <v>28268.41</v>
+        <v>56.280000000000001</v>
       </c>
       <c r="M25" s="0">
-        <v>73.293000000000006</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="26">
@@ -1265,40 +1232,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>1043583453</v>
+        <v>7558522549</v>
       </c>
       <c r="C26" s="0">
-        <v>1575251693</v>
+        <v>15224529400</v>
       </c>
       <c r="D26" s="0">
-        <v>365488</v>
+        <v>880031</v>
       </c>
       <c r="E26" s="0">
-        <v>178</v>
+        <v>261</v>
       </c>
       <c r="F26" s="0">
-        <v>8899</v>
+        <v>12242</v>
       </c>
       <c r="G26" s="0">
-        <v>2.0600000000000001</v>
+        <v>0.70999999999999996</v>
       </c>
       <c r="H26" s="0">
-        <v>5.4900000000000002</v>
+        <v>6.75</v>
       </c>
       <c r="I26" s="0">
-        <v>66.25</v>
+        <v>49.649999999999999</v>
       </c>
       <c r="J26" s="0">
-        <v>992</v>
+        <v>4832</v>
       </c>
       <c r="K26" s="0">
-        <v>7540.5900000000001</v>
+        <v>14359.98</v>
       </c>
       <c r="L26" s="0">
-        <v>42.270000000000003</v>
+        <v>55.759999999999998</v>
       </c>
       <c r="M26" s="0">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="27">
@@ -1306,40 +1273,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>32660225447</v>
+        <v>3066967260</v>
       </c>
       <c r="C27" s="0">
-        <v>56047238877</v>
+        <v>7734723540</v>
       </c>
       <c r="D27" s="0">
-        <v>462398</v>
+        <v>1670567</v>
       </c>
       <c r="E27" s="0">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="F27" s="0">
-        <v>244968</v>
+        <v>6484</v>
       </c>
       <c r="G27" s="0">
-        <v>2.02</v>
+        <v>1.3999999999999999</v>
       </c>
       <c r="H27" s="0">
-        <v>6.4100000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="I27" s="0">
-        <v>58.270000000000003</v>
+        <v>39.649999999999999</v>
       </c>
       <c r="J27" s="0">
-        <v>1278</v>
+        <v>3751</v>
       </c>
       <c r="K27" s="0">
-        <v>4849.1999999999998</v>
+        <v>8714.9200000000001</v>
       </c>
       <c r="L27" s="0">
-        <v>27.09</v>
+        <v>27.41</v>
       </c>
       <c r="M27" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="28">
@@ -1347,40 +1314,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>13157247322</v>
+        <v>14259736782</v>
       </c>
       <c r="C28" s="0">
-        <v>21851085570</v>
+        <v>22303477341</v>
       </c>
       <c r="D28" s="0">
-        <v>0</v>
+        <v>550160</v>
       </c>
       <c r="E28" s="0">
-        <v>186</v>
+        <v>301</v>
       </c>
       <c r="F28" s="0">
-        <v>80157</v>
+        <v>22799</v>
       </c>
       <c r="G28" s="0">
-        <v>0</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H28" s="0">
-        <v>0</v>
+        <v>3.9199999999999999</v>
       </c>
       <c r="I28" s="0">
-        <v>60.210000000000001</v>
+        <v>63.939999999999998</v>
       </c>
       <c r="J28" s="0">
-        <v>1484</v>
+        <v>3366</v>
       </c>
       <c r="K28" s="0">
-        <v>6082.7600000000002</v>
+        <v>13874.34</v>
       </c>
       <c r="L28" s="0">
-        <v>33.060000000000002</v>
+        <v>47.590000000000003</v>
       </c>
       <c r="M28" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.099000000000000005</v>
       </c>
     </row>
     <row r="29">
@@ -1388,40 +1355,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>3872373763</v>
+        <v>6517876044</v>
       </c>
       <c r="C29" s="0">
-        <v>6172407107</v>
+        <v>11724723131</v>
       </c>
       <c r="D29" s="0">
-        <v>458915</v>
+        <v>934241</v>
       </c>
       <c r="E29" s="0">
-        <v>234</v>
+        <v>306</v>
       </c>
       <c r="F29" s="0">
-        <v>19128</v>
+        <v>7956</v>
       </c>
       <c r="G29" s="0">
-        <v>1.4199999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="0">
-        <v>4.7800000000000002</v>
+        <v>6</v>
       </c>
       <c r="I29" s="0">
-        <v>62.740000000000002</v>
+        <v>55.590000000000003</v>
       </c>
       <c r="J29" s="0">
-        <v>1380</v>
+        <v>4744</v>
       </c>
       <c r="K29" s="0">
-        <v>6560.54</v>
+        <v>20396.029999999999</v>
       </c>
       <c r="L29" s="0">
-        <v>28.050000000000001</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="M29" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.13100000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1429,491 +1396,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>7556513617</v>
+        <v>205776074655</v>
       </c>
       <c r="C30" s="0">
-        <v>11549571538</v>
+        <v>344178252783</v>
       </c>
       <c r="D30" s="0">
-        <v>361376</v>
+        <v>420920</v>
       </c>
       <c r="E30" s="0">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="F30" s="0">
-        <v>20732</v>
+        <v>1580443</v>
       </c>
       <c r="G30" s="0">
-        <v>0.65000000000000002</v>
+        <v>1.9299999999999999</v>
       </c>
       <c r="H30" s="0">
-        <v>3.75</v>
+        <v>5.7300000000000004</v>
       </c>
       <c r="I30" s="0">
-        <v>65.430000000000007</v>
+        <v>59.789999999999999</v>
       </c>
       <c r="J30" s="0">
-        <v>2632</v>
+        <v>1177</v>
       </c>
       <c r="K30" s="0">
-        <v>8337.2000000000007</v>
+        <v>7080.2600000000002</v>
       </c>
       <c r="L30" s="0">
-        <v>39.380000000000003</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="M30" s="0">
-        <v>0.085999999999999993</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="0">
-        <v>2665252729</v>
-      </c>
-      <c r="C31" s="0">
-        <v>4329066272</v>
-      </c>
-      <c r="D31" s="0">
-        <v>0</v>
-      </c>
-      <c r="E31" s="0">
-        <v>238</v>
-      </c>
-      <c r="F31" s="0">
-        <v>6200</v>
-      </c>
-      <c r="G31" s="0">
-        <v>0</v>
-      </c>
-      <c r="H31" s="0">
-        <v>0</v>
-      </c>
-      <c r="I31" s="0">
-        <v>61.57</v>
-      </c>
-      <c r="J31" s="0">
-        <v>2934</v>
-      </c>
-      <c r="K31" s="0">
-        <v>7817.4399999999996</v>
-      </c>
-      <c r="L31" s="0">
-        <v>32.850000000000001</v>
-      </c>
-      <c r="M31" s="0">
-        <v>0.070999999999999994</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="0">
-        <v>4799955587</v>
-      </c>
-      <c r="C32" s="0">
-        <v>7642475656</v>
-      </c>
-      <c r="D32" s="0">
-        <v>557032</v>
-      </c>
-      <c r="E32" s="0">
-        <v>254</v>
-      </c>
-      <c r="F32" s="0">
-        <v>9764</v>
-      </c>
-      <c r="G32" s="0">
-        <v>0.70999999999999996</v>
-      </c>
-      <c r="H32" s="0">
-        <v>4.7199999999999998</v>
-      </c>
-      <c r="I32" s="0">
-        <v>62.810000000000002</v>
-      </c>
-      <c r="J32" s="0">
-        <v>3086</v>
-      </c>
-      <c r="K32" s="0">
-        <v>10698.76</v>
-      </c>
-      <c r="L32" s="0">
-        <v>42.189999999999998</v>
-      </c>
-      <c r="M32" s="0">
-        <v>0.090999999999999998</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="0">
-        <v>5094388946</v>
-      </c>
-      <c r="C33" s="0">
-        <v>9550626252</v>
-      </c>
-      <c r="D33" s="0">
-        <v>816293</v>
-      </c>
-      <c r="E33" s="0">
-        <v>289</v>
-      </c>
-      <c r="F33" s="0">
-        <v>9177</v>
-      </c>
-      <c r="G33" s="0">
-        <v>0.78000000000000003</v>
-      </c>
-      <c r="H33" s="0">
-        <v>5.9299999999999997</v>
-      </c>
-      <c r="I33" s="0">
-        <v>53.340000000000003</v>
-      </c>
-      <c r="J33" s="0">
-        <v>3603</v>
-      </c>
-      <c r="K33" s="0">
-        <v>8768.4799999999996</v>
-      </c>
-      <c r="L33" s="0">
-        <v>30.350000000000001</v>
-      </c>
-      <c r="M33" s="0">
-        <v>0.064000000000000001</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="0">
-        <v>773571332</v>
-      </c>
-      <c r="C34" s="0">
-        <v>1830084789</v>
-      </c>
-      <c r="D34" s="0">
-        <v>871469</v>
-      </c>
-      <c r="E34" s="0">
-        <v>277</v>
-      </c>
-      <c r="F34" s="0">
-        <v>1345</v>
-      </c>
-      <c r="G34" s="0">
-        <v>0.64000000000000001</v>
-      </c>
-      <c r="H34" s="0">
-        <v>6.4000000000000004</v>
-      </c>
-      <c r="I34" s="0">
-        <v>42.270000000000003</v>
-      </c>
-      <c r="J34" s="0">
-        <v>4912</v>
-      </c>
-      <c r="K34" s="0">
-        <v>9192.6700000000001</v>
-      </c>
-      <c r="L34" s="0">
-        <v>33.189999999999998</v>
-      </c>
-      <c r="M34" s="0">
-        <v>0.068000000000000005</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="0">
-        <v>2604399457</v>
-      </c>
-      <c r="C35" s="0">
-        <v>6084918714</v>
-      </c>
-      <c r="D35" s="0">
-        <v>1236772</v>
-      </c>
-      <c r="E35" s="0">
-        <v>302</v>
-      </c>
-      <c r="F35" s="0">
-        <v>3626</v>
-      </c>
-      <c r="G35" s="0">
-        <v>0.73999999999999999</v>
-      </c>
-      <c r="H35" s="0">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="I35" s="0">
-        <v>42.799999999999997</v>
-      </c>
-      <c r="J35" s="0">
-        <v>5549</v>
-      </c>
-      <c r="K35" s="0">
-        <v>10350.969999999999</v>
-      </c>
-      <c r="L35" s="0">
-        <v>34.219999999999999</v>
-      </c>
-      <c r="M35" s="0">
-        <v>0.067000000000000004</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="0">
-        <v>3315797016</v>
-      </c>
-      <c r="C36" s="0">
-        <v>7317275196</v>
-      </c>
-      <c r="D36" s="0">
-        <v>715276</v>
-      </c>
-      <c r="E36" s="0">
-        <v>229</v>
-      </c>
-      <c r="F36" s="0">
-        <v>9472</v>
-      </c>
-      <c r="G36" s="0">
-        <v>0.93000000000000005</v>
-      </c>
-      <c r="H36" s="0">
-        <v>6.4400000000000004</v>
-      </c>
-      <c r="I36" s="0">
-        <v>45.310000000000002</v>
-      </c>
-      <c r="J36" s="0">
-        <v>3420</v>
-      </c>
-      <c r="K36" s="0">
-        <v>12721.77</v>
-      </c>
-      <c r="L36" s="0">
-        <v>56.280000000000001</v>
-      </c>
-      <c r="M36" s="0">
-        <v>0.115</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="0">
-        <v>7558522549</v>
-      </c>
-      <c r="C37" s="0">
-        <v>15224529400</v>
-      </c>
-      <c r="D37" s="0">
-        <v>880031</v>
-      </c>
-      <c r="E37" s="0">
-        <v>261</v>
-      </c>
-      <c r="F37" s="0">
-        <v>12242</v>
-      </c>
-      <c r="G37" s="0">
-        <v>0.70999999999999996</v>
-      </c>
-      <c r="H37" s="0">
-        <v>6.75</v>
-      </c>
-      <c r="I37" s="0">
-        <v>49.649999999999999</v>
-      </c>
-      <c r="J37" s="0">
-        <v>4832</v>
-      </c>
-      <c r="K37" s="0">
-        <v>14359.98</v>
-      </c>
-      <c r="L37" s="0">
-        <v>55.759999999999998</v>
-      </c>
-      <c r="M37" s="0">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="0">
-        <v>3066967260</v>
-      </c>
-      <c r="C38" s="0">
-        <v>7734723540</v>
-      </c>
-      <c r="D38" s="0">
-        <v>1670567</v>
-      </c>
-      <c r="E38" s="0">
-        <v>318</v>
-      </c>
-      <c r="F38" s="0">
-        <v>6484</v>
-      </c>
-      <c r="G38" s="0">
-        <v>1.3999999999999999</v>
-      </c>
-      <c r="H38" s="0">
-        <v>10.49</v>
-      </c>
-      <c r="I38" s="0">
-        <v>39.649999999999999</v>
-      </c>
-      <c r="J38" s="0">
-        <v>3751</v>
-      </c>
-      <c r="K38" s="0">
-        <v>8718.8600000000006</v>
-      </c>
-      <c r="L38" s="0">
-        <v>27.420000000000002</v>
-      </c>
-      <c r="M38" s="0">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="0">
-        <v>14259736782</v>
-      </c>
-      <c r="C39" s="0">
-        <v>22303477341</v>
-      </c>
-      <c r="D39" s="0">
-        <v>550160</v>
-      </c>
-      <c r="E39" s="0">
-        <v>301</v>
-      </c>
-      <c r="F39" s="0">
-        <v>22799</v>
-      </c>
-      <c r="G39" s="0">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H39" s="0">
-        <v>3.9199999999999999</v>
-      </c>
-      <c r="I39" s="0">
-        <v>63.939999999999998</v>
-      </c>
-      <c r="J39" s="0">
-        <v>3366</v>
-      </c>
-      <c r="K39" s="0">
-        <v>13874.34</v>
-      </c>
-      <c r="L39" s="0">
-        <v>47.590000000000003</v>
-      </c>
-      <c r="M39" s="0">
-        <v>0.099000000000000005</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="0">
-        <v>6517876044</v>
-      </c>
-      <c r="C40" s="0">
-        <v>11724723131</v>
-      </c>
-      <c r="D40" s="0">
-        <v>934241</v>
-      </c>
-      <c r="E40" s="0">
-        <v>306</v>
-      </c>
-      <c r="F40" s="0">
-        <v>7956</v>
-      </c>
-      <c r="G40" s="0">
-        <v>0.63</v>
-      </c>
-      <c r="H40" s="0">
-        <v>6</v>
-      </c>
-      <c r="I40" s="0">
-        <v>55.590000000000003</v>
-      </c>
-      <c r="J40" s="0">
-        <v>4744</v>
-      </c>
-      <c r="K40" s="0">
-        <v>20396.029999999999</v>
-      </c>
-      <c r="L40" s="0">
-        <v>65.739999999999995</v>
-      </c>
-      <c r="M40" s="0">
-        <v>0.13100000000000001</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="0">
-        <v>377832386989</v>
-      </c>
-      <c r="C41" s="0">
-        <v>645433587063</v>
-      </c>
-      <c r="D41" s="0">
-        <v>0</v>
-      </c>
-      <c r="E41" s="0">
-        <v>129</v>
-      </c>
-      <c r="F41" s="0">
-        <v>5000083</v>
-      </c>
-      <c r="G41" s="0">
-        <v>0</v>
-      </c>
-      <c r="H41" s="0">
-        <v>0</v>
-      </c>
-      <c r="I41" s="0">
-        <v>58.539999999999999</v>
-      </c>
-      <c r="J41" s="0">
-        <v>837</v>
-      </c>
-      <c r="K41" s="0">
-        <v>4895.54</v>
-      </c>
-      <c r="L41" s="0">
-        <v>33.549999999999997</v>
-      </c>
-      <c r="M41" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
   </sheetData>
